--- a/Doc/FGJ 2026表格_v2.xlsx
+++ b/Doc/FGJ 2026表格_v2.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -49,6 +49,9 @@
       <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -86,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +105,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -310,25 +315,22 @@
   <commentList>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
-        <t>填門檻值，屬性 ≥ 此值算達標；0＝此屬性必須未達標
+        <t>條件字串，格式同 require，例：mor&gt;=10、mor&lt;=-10、spd&gt;=20
+空白＝中立／未達標
 （詳見「格式說明」分頁）</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
-        <t>填門檻值，屬性 ≥ 此值算達標；0＝此屬性必須未達標
+        <t>條件字串，格式同 require，例：mor&gt;=10、mor&lt;=-10、spd&gt;=20
+空白＝中立／未達標
 （詳見「格式說明」分頁）</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
-        <t>填門檻值，屬性 ≥ 此值算達標；0＝此屬性必須未達標
-（詳見「格式說明」分頁）</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t>填門檻值，屬性 ≥ 此值算達標；0＝此屬性必須未達標
+        <t>條件字串，格式同 require，例：mor&gt;=10、mor&lt;=-10、spd&gt;=20
+空白＝中立／未達標
 （詳見「格式說明」分頁）</t>
       </text>
     </comment>
@@ -3737,133 +3739,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>稱號ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>稱號名稱</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>稱號圖片</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>善惡達標</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>濕度達標</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>速度達標</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>韌度達標</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>title_id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>title_name</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>title_image</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>reach_mor</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>reach_hmd</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>reach_spd</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>reach_tgh</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n"/>
+      <c r="G2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -3879,19 +3868,7 @@
           <t>title_0</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>全部未達標（無為的草）</t>
         </is>
@@ -3903,7 +3880,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>善良的草</t>
+          <t>很會跑的草</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3911,17 +3888,10 @@
           <t>title_1</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3930,7 +3900,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>水嫩的草</t>
+          <t>頑強的草</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3938,17 +3908,10 @@
           <t>title_2</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3957,7 +3920,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>很會跑的草</t>
+          <t>運動健將的草</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3965,17 +3928,15 @@
           <t>title_3</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3984,7 +3945,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>頑強的草</t>
+          <t>善良的草</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3992,17 +3953,10 @@
           <t>title_4</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>mor&gt;=10</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4011,7 +3965,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>溫柔多汁的草</t>
+          <t>熱心快遞的草</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4019,17 +3973,15 @@
           <t>title_5</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mor&gt;=10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4038,7 +3990,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>熱心快遞的草</t>
+          <t>守護大家的草</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4046,17 +3998,15 @@
           <t>title_6</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mor&gt;=10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -4065,7 +4015,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>守護大家的草</t>
+          <t>英雄般的草</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4073,17 +4023,20 @@
           <t>title_7</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>20</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mor&gt;=10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4092,7 +4045,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>水上漂的草</t>
+          <t>壞心眼的草</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4100,17 +4053,10 @@
           <t>title_8</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>20</v>
-      </c>
-      <c r="F12" t="n">
-        <v>20</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>mor&lt;=-10</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4119,7 +4065,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>泡不爛的草</t>
+          <t>偷了就跑的草</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4127,17 +4073,15 @@
           <t>title_9</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mor&lt;=-10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4146,7 +4090,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>運動健將的草</t>
+          <t>橫行霸道的草</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4154,17 +4098,15 @@
           <t>title_10</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G14" t="n">
-        <v>20</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mor&lt;=-10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -4173,7 +4115,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>及時雨的草</t>
+          <t>大魔王般的草</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4181,142 +4123,117 @@
           <t>title_11</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mor&lt;=-10</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>12</v>
+        <v>2008</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>大樹般的草</t>
+          <t>標本裡的草</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>title_12</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="n">
-        <v>20</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20</v>
+          <t>title_2008</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>13</v>
+        <v>2009</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>英雄般的草</t>
+          <t>成為兔子晚餐的草</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>title_13</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>20</v>
-      </c>
-      <c r="G17" t="n">
-        <v>20</v>
+          <t>title_2009</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>14</v>
+        <v>2010</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>野性十足的草</t>
+          <t>花瓶裡的草</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>title_14</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>20</v>
-      </c>
-      <c r="F18" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
+          <t>title_2010</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>15</v>
+        <v>3015</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>傳說中的草</t>
+          <t>飛上天的草</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>title_15</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" t="n">
-        <v>20</v>
+          <t>title_3015</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>2008</v>
+        <v>3016</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>標本裡的草</t>
+          <t>柏油縫裡的草</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>title_2008</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+          <t>title_3016</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -4324,19 +4241,19 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>2009</v>
+        <v>3017</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>成為兔子晚餐的草</t>
+          <t>開花的草</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>title_2009</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+          <t>title_3017</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -4344,19 +4261,19 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>2010</v>
+        <v>3018</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>花瓶裡的草</t>
+          <t>變成茶的草</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>title_2010</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+          <t>title_3018</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -4364,19 +4281,19 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>3015</v>
+        <v>3019</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>飛上天的草</t>
+          <t>變成草蜢的草</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>title_3015</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+          <t>title_3019</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -4384,19 +4301,19 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>3016</v>
+        <v>3020</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>柏油縫裡的草</t>
+          <t>游向大海的草</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>title_3016</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+          <t>title_3020</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -4404,89 +4321,9 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>3017</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>開花的草</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>title_3017</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>特殊結局</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>3018</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>變成茶的草</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>title_3018</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>特殊結局</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>3019</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>變成草蜢的草</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>title_3019</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>特殊結局</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>3020</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>游向大海的草</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>title_3020</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>特殊結局</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
         <v>3021</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>特殊結局（備用）</t>
         </is>
@@ -4795,7 +4632,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -4899,7 +4735,6 @@
       </c>
       <c r="C14" s="9" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -5148,7 +4983,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="16.5" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
@@ -5296,7 +5130,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45" ht="16.5" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
@@ -5376,7 +5209,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52" ht="16.5" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
@@ -5459,7 +5291,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60" ht="16.5" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
@@ -5550,7 +5381,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="16.5" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
@@ -5582,7 +5412,7 @@
       <c r="B69" s="9" t="inlineStr">
         <is>
           <t>1. 遊戲中選了有 end 的選項 → 給該特殊結局稱號
-2. 否則結算時看屬性達標 → 找 reach_* 四欄完全吻合的那一列</t>
+2. 否則結算時看屬性 → 找 reach_* 三欄都吻合的那一列</t>
         </is>
       </c>
     </row>
@@ -5594,19 +5424,19 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>填該屬性的門檻值；0＝此屬性必須「未達標」</t>
+          <t>填條件字串，格式同 require（例：mor&gt;=10）；空白＝中立／未達標</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>達標條件</t>
+          <t>吻合規則</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>結算時屬性 ≥ 門檻值就算達標；找出「達標的屬性」與 reach_* 非 0 欄位完全一致的那一列</t>
+          <t>有填的條件都要成立；空白欄的屬性不可符合該欄出現過的任何條件（mor 空白＝不善也不惡）</t>
         </is>
       </c>
     </row>
@@ -5618,19 +5448,19 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>四個屬性都未達標＝無為的草</t>
+          <t>三欄皆空白＝無為的草</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>ID 1～15</t>
+          <t>ID 0～11</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>其餘 15 種達標組合，不可重複、不可缺漏</t>
+          <t>善惡 3 種（善／中立／惡）× 速度 2 種 × 韌度 2 種 = 12 種組合，不可重複、不可缺漏</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5476,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76" ht="16.5" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
@@ -5657,14 +5486,14 @@
       <c r="C76" s="7" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>屬性</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>門檻值</t>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>條件</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -5672,64 +5501,63 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>mor</t>
+          <t>善</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>≥ 10</t>
+          <t>mor&gt;=10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>hmd</t>
+          <t>惡</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>≥ 20</t>
+          <t>mor&lt;=-10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>spd</t>
+          <t>速度達標</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>≥ 20</t>
+          <t>spd&gt;=20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>tgh</t>
+          <t>韌度達標</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>≥ 20</t>
+          <t>tgh&gt;=20</t>
         </is>
       </c>
     </row>
     <row r="82" ht="25.5" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>待確認</t>
+          <t>濕度</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>目前 mor ≥ 10（善）才算達標，邪惡（負數）不算達標</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
+          <t>不列入稱號判定（濕度是遊戲結束條件）</t>
+        </is>
+      </c>
+    </row>
     <row r="84" ht="16.5" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>

--- a/Doc/FGJ 2026表格_v2.xlsx
+++ b/Doc/FGJ 2026表格_v2.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,6 +154,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1302,7 +1303,7 @@
         </is>
       </c>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="19" t="inlineStr">
         <is>
           <t>mor:-10;spd:+5</t>
         </is>
@@ -1658,7 +1659,7 @@
         </is>
       </c>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="19" t="inlineStr">
         <is>
           <t>mor:-5;spd:+10</t>
         </is>
@@ -1902,11 +1903,7 @@
           <t>混進菜苗裡假裝是蔬菜</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>mor&lt;=-5</t>
-        </is>
-      </c>
+      <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>mor:-5;hmd:+10</t>
@@ -2025,7 +2022,11 @@
           <t>伸長葉子撈起被沖走的瓢蟲</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>mor&gt;=-10</t>
+        </is>
+      </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
           <t>mor:+10;hmd:-20</t>
@@ -2114,7 +2115,11 @@
           <t>跟麻雀一起偷吃稻穀</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>mor&lt;=10</t>
+        </is>
+      </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
           <t>mor:-10;hmd:-20;tgh:+5</t>
@@ -2133,18 +2138,18 @@
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="10" t="inlineStr">
         <is>
-          <t>爬上稻草人的斗笠眺望遠方</t>
+          <t>踩扁稻草人的斗笠</t>
         </is>
       </c>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>hmd:-20;spd:+5</t>
+          <t>mor:-5;hmd:-20;spd:+5</t>
         </is>
       </c>
       <c r="U16" s="10" t="inlineStr">
         <is>
-          <t>你看清了前面的路，斗笠上卻曬得要命。</t>
+          <t>你踩著斗笠跳得老高，看清了前面的路。稻草人被你弄得歪七扭八，太陽也曬得你發暈。</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
@@ -2181,11 +2186,7 @@
           <t>乖乖等紅綠燈</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>mor&gt;=0</t>
-        </is>
-      </c>
+      <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
           <t>mor:+5;tgh:+5</t>
@@ -2375,11 +2376,7 @@
           <t>過去跟牧羊犬交朋友</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>mor&gt;=5</t>
-        </is>
-      </c>
+      <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
           <t>mor:+5;hmd:+10</t>
@@ -2420,18 +2417,18 @@
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="10" t="inlineStr">
         <is>
-          <t>在狗面前裝成一根枯草</t>
+          <t>騙牧羊犬去追兔子</t>
         </is>
       </c>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>hmd:-20;tgh:+5</t>
+          <t>mor:-10;hmd:-20</t>
         </is>
       </c>
       <c r="U19" s="10" t="inlineStr">
         <is>
-          <t>裝得太像了，連你自己都真的有點乾了。</t>
+          <t>牧羊犬被你騙得團團轉，羊群亂成一團。你在太陽下笑到葉子都乾了。</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr">
@@ -2516,11 +2513,7 @@
           <t>搶走青蛙的地盤</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>mor&lt;=-5</t>
-        </is>
-      </c>
+      <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="inlineStr">
         <is>
           <t>mor:-10;hmd:-20;tgh:+10</t>
@@ -2959,7 +2952,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>mor&lt;=-5</t>
+          <t>mor&lt;=10</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2983,7 +2976,11 @@
           <t>幫牠趕走啃牠的蜥蜴</t>
         </is>
       </c>
-      <c r="S25" s="4" t="n"/>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>mor&gt;=-10</t>
+        </is>
+      </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
           <t>mor:+10;hmd:-10</t>
@@ -3073,18 +3070,18 @@
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="10" t="inlineStr">
         <is>
-          <t>幫一隻迷路的麻雀找媽媽</t>
+          <t>把迷路的麻雀趕得更遠</t>
         </is>
       </c>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>mor:+10;hmd:-10</t>
+          <t>mor:-10;hmd:-10</t>
         </is>
       </c>
       <c r="U26" s="10" t="inlineStr">
         <is>
-          <t>麻雀媽媽找到了，你在烈日下陪牠找了一整條街。</t>
+          <t>麻雀嚇得飛走了。你在烈日下得意了好久，葉子都曬乾了。</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr">
@@ -3171,7 +3168,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>mor&lt;=-10</t>
+          <t>mor&lt;=10</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr">
@@ -3244,11 +3241,7 @@
           <t>幫牠搔下巴</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>mor&gt;=0</t>
-        </is>
-      </c>
+      <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>mor:+5;hmd:-10</t>
@@ -3456,7 +3449,11 @@
           <t>把麵包屑讓給搶不到的雛鳥</t>
         </is>
       </c>
-      <c r="S30" s="4" t="n"/>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>mor&gt;=-10</t>
+        </is>
+      </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
           <t>mor:+10;hmd:-10</t>
@@ -3550,18 +3547,18 @@
       <c r="Q31" s="3" t="n"/>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>救出被困在車底的蟋蟀</t>
+          <t>把蟋蟀踢進車底</t>
         </is>
       </c>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="4" t="inlineStr">
         <is>
-          <t>mor:+10;hmd:-10</t>
+          <t>mor:-10;hmd:-10</t>
         </is>
       </c>
       <c r="U31" s="10" t="inlineStr">
         <is>
-          <t>蟋蟀出來了，牠說晚上要為你唱歌。</t>
+          <t>蟋蟀在車底叫個不停，你頭也不回地走了。地面燙得你直冒煙。</t>
         </is>
       </c>
       <c r="V31" s="4" t="inlineStr">
@@ -3622,7 +3619,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>mor&lt;=-10</t>
+          <t>mor&lt;=10</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3646,7 +3643,11 @@
           <t>提醒小螞蟻不要踩到水泥</t>
         </is>
       </c>
-      <c r="S32" s="4" t="n"/>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>mor&gt;=-10</t>
+        </is>
+      </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
           <t>mor:+10;hmd:-10</t>
@@ -3810,11 +3811,7 @@
           <t>偷吃一口粉圓</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>mor&lt;=-5</t>
-        </is>
-      </c>
+      <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
           <t>mor:-5;hmd:-10;spd:+10</t>
@@ -3836,7 +3833,11 @@
           <t>幫攤販趕蒼蠅</t>
         </is>
       </c>
-      <c r="S34" s="4" t="n"/>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>mor&gt;=-10</t>
+        </is>
+      </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
           <t>mor:+10;hmd:-10</t>
@@ -3926,18 +3927,18 @@
       <c r="Q35" s="3" t="n"/>
       <c r="R35" s="10" t="inlineStr">
         <is>
-          <t>把掉出巢的雛鳥推回去</t>
+          <t>偷吃鳥巢裡的蟲</t>
         </is>
       </c>
       <c r="S35" s="4" t="n"/>
       <c r="T35" s="4" t="inlineStr">
         <is>
-          <t>mor:+10;hmd:-10</t>
+          <t>mor:-5;hmd:-10</t>
         </is>
       </c>
       <c r="U35" s="10" t="inlineStr">
         <is>
-          <t>鳥媽媽回來時，雛鳥正好好地待在巢裡。</t>
+          <t>蟲子很好吃，鳥媽媽回來時氣得直叫。鐵皮屋頂曬得你頭昏眼花。</t>
         </is>
       </c>
       <c r="V35" s="4" t="inlineStr">
@@ -4019,18 +4020,18 @@
       <c r="Q36" s="3" t="n"/>
       <c r="R36" s="10" t="inlineStr">
         <is>
-          <t>幫招潮蟹找回掉了的大螯</t>
+          <t>把招潮蟹的大螯藏起來</t>
         </is>
       </c>
       <c r="S36" s="4" t="n"/>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>mor:+10;hmd:-10</t>
+          <t>mor:-5;hmd:-10</t>
         </is>
       </c>
       <c r="U36" s="10" t="inlineStr">
         <is>
-          <t>招潮蟹裝回大螯，對你行了個禮。</t>
+          <t>招潮蟹找了一整個下午，你躲在鹽堆後面偷笑，被曬得好乾。</t>
         </is>
       </c>
       <c r="V36" s="4" t="inlineStr">
@@ -4117,7 +4118,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>mor&lt;=-5</t>
+          <t>mor&lt;=10</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr">
@@ -4476,7 +4477,7 @@
       <c r="Q41" s="3" t="n"/>
       <c r="R41" s="10" t="inlineStr">
         <is>
-          <t>趁她不注意快跑</t>
+          <t>趁他不注意快跑</t>
         </is>
       </c>
       <c r="S41" s="4" t="n"/>
@@ -4842,9 +4843,9 @@
           <t>title_1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
         </is>
       </c>
     </row>
@@ -4862,9 +4863,9 @@
           <t>title_2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
         </is>
       </c>
     </row>
@@ -4882,14 +4883,14 @@
           <t>title_3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
         </is>
       </c>
     </row>
@@ -4932,9 +4933,9 @@
           <t>mor&gt;=10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
         </is>
       </c>
     </row>
@@ -4957,9 +4958,9 @@
           <t>mor&gt;=10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
         </is>
       </c>
     </row>
@@ -4982,14 +4983,14 @@
           <t>mor&gt;=10</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
         </is>
       </c>
     </row>
@@ -5032,9 +5033,9 @@
           <t>mor&lt;=-10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
         </is>
       </c>
     </row>
@@ -5057,9 +5058,9 @@
           <t>mor&lt;=-10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
         </is>
       </c>
     </row>
@@ -5082,14 +5083,14 @@
           <t>mor&lt;=-10</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5284,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="13.5" customHeight="1">
       <c r="I32" s="14" t="n"/>
     </row>
@@ -5313,13 +5308,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="B2:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5356,8 +5350,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="C8" s="1" t="inlineStr">
         <is>
@@ -5526,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5607,7 +5599,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -5634,7 +5625,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="25.5" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>mor</t>
@@ -5711,7 +5702,6 @@
       </c>
       <c r="C14" s="9" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -5960,7 +5950,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="16.5" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
@@ -6108,516 +6097,535 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>善良值需求原則</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>±5 的小事不設需求；+10 的善事設 mor&gt;=-10（太邪惡就不肯幫忙）；-10 的壞事設 mor&lt;=10（太善良就下不了手）；-15 以上的大壞事設 mor&lt;=-5（越陷越深）</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="16.5" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>至少一個可選</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>每個事件至少要有一個沒有需求的選項，避免三個都鎖住</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>五、結局 choice_x_end</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>範例</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>填 title_list 的 title_id（整數）</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>觸發</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>選了這個選項就直接結束遊戲，給該稱號</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>沒有結局</t>
+          <t>內容</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>留空</t>
+          <t>填 title_list 的 title_id（整數）</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>2008</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
+          <t>觸發</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>選了這個選項就直接結束遊戲，給該稱號</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>沒有結局</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16.5" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
           <t>對應</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>填的 ID 必須存在於 title_list</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="54" ht="25.5" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>六、event_list 其他欄位</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="7" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
-      <c r="C53" s="8" t="n"/>
-    </row>
-    <row r="54" ht="25.5" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>事件 ID，千位數＝階段（1xxx 第 1 階段、2xxx 第 2 階段、3xxx 第 3 階段），不可重複</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>unlock_event_num</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>解鎖所需事件數：已經歷 N 個事件後，此事件才會進入抽選池</t>
-        </is>
-      </c>
+      <c r="C55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>event_desc</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>事件敘述（題目本身）（不限字數）</t>
+          <t>事件 ID，千位數＝階段（1xxx 第 1 階段、2xxx 第 2 階段、3xxx 第 3 階段），不可重複</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25.5" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>choice_x_desc</t>
+          <t>unlock_event_num</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>選項文案：最多 14 字（含標點符號，剛好 14 字可以），只暗示需求與後果，不直接寫數值。只有這三欄有字數限制</t>
+          <t>解鎖所需事件數：已經歷 N 個事件後，此事件才會進入抽選池</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>choice_x_result</t>
+          <t>event_desc</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>選後回饋：選完後顯示的微敘事＋提示，例「你變得更溼潤了，前方乾燥地帶可能更難」（不限字數）</t>
+          <t>事件敘述（題目本身）（不限字數）</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>event_image</t>
+          <t>choice_x_desc</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>事件發生時顯示的圖片。命名：event_{事件ID}，例 event_1001，不含副檔名。圖片由 Codex image generate 產生</t>
+          <t>選項文案：最多 14 字（含標點符號，剛好 14 字可以），只暗示需求與後果，不直接寫數值。只有這三欄有字數限制</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
+          <t>choice_x_result</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>選後回饋：選完後顯示的微敘事＋提示，例「你變得更溼潤了，前方乾燥地帶可能更難」（不限字數）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>event_image</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>事件發生時顯示的圖片。命名：event_{事件ID}，例 event_1001，不含副檔名。圖片由 Codex image generate 產生</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16.5" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
           <t>choice_x_image</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>選完該選項後顯示的圖片。命名：event_{事件ID}_{a/b/c}，例 event_1001_a，不含副檔名；結局選項的圖也填這裡。圖片由 Codex image generate 產生</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62" ht="16.5" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>七、階段規則（濕度）</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>階段</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>解鎖所需事件數</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>必須減少濕度的選項（offset 要有 hmd:-xx）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>1（1xxx）</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>2（2xxx）</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>B、C</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>3（3xxx）</t>
+          <t>1（1xxx）</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>A、B、C</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
+          <t>2（2xxx）</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>B、C</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>3（3xxx）</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>A、B、C</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="25.5" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>有填 end 的特殊結局選項不受此限</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69" ht="25.5" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="71" ht="25.5" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>八、稱號 title_list</t>
         </is>
       </c>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
-      <c r="C70" s="8" t="n"/>
-    </row>
-    <row r="71" ht="25.5" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="C72" s="8" t="n"/>
+    </row>
+    <row r="73" ht="25.5" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>判定順序</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>1. 遊戲中選了有 end 的選項 → 給該特殊結局稱號
 2. 否則結算時看屬性 → 找 reach_* 三欄都吻合的那一列</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>reach_*</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>填條件字串，格式同 require（例：mor&gt;=10）；空白＝中立／未達標</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="25.5" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>吻合規則</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>有填的條件都要成立；空白欄的屬性不可符合該欄出現過的任何條件（mor 空白＝不善也不惡）</t>
-        </is>
-      </c>
-    </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>ID 0</t>
+          <t>reach_*</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>三欄皆空白＝無為的草</t>
+          <t>填條件字串，格式同 require（例：mor&gt;=10）；空白＝中立／未達標</t>
         </is>
       </c>
     </row>
     <row r="75" ht="25.5" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>ID 0～11</t>
+          <t>吻合規則</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>善良值 3 種（善／中立／惡）× 速度 2 種 × 韌度 2 種 = 12 種組合，不可重複、不可缺漏</t>
+          <t>有填的條件都要成立；空白欄的屬性不可符合該欄出現過的任何條件（mor 空白＝不善也不惡）</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
+          <t>ID 0</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>三欄皆空白＝無為的草</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>ID 0～11</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>善良值 3 種（善／中立／惡）× 速度 2 種 × 韌度 2 種 = 12 種組合，不可重複、不可缺漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16.5" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
           <t>特殊結局</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>ID 與觸發它的事件 ID 相同（如 2008）；reach_* 留空；3021 為備用</t>
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78" ht="16.5" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>九、達標門檻（依 title_list 的 reach_*）</t>
         </is>
       </c>
-      <c r="B78" s="7" t="n"/>
-      <c r="C78" s="7" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="B80" s="7" t="n"/>
+      <c r="C80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>條件</t>
         </is>
       </c>
-      <c r="C79" s="8" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>善</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>mor&gt;=10</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>惡</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>mor&lt;=-10</t>
-        </is>
-      </c>
+      <c r="C81" s="8" t="n"/>
     </row>
     <row r="82" ht="25.5" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>速度達標</t>
+          <t>善</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>spd&gt;=20</t>
+          <t>mor&gt;=10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>韌度達標</t>
+          <t>惡</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>tgh&gt;=20</t>
+          <t>mor&lt;=-10</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
+          <t>速度達標</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>spd&gt;=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>韌度達標</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>tgh&gt;=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16.5" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
           <t>濕度</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>不列入稱號判定（濕度是遊戲結束條件）</t>
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86" ht="16.5" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="87" ht="25.5" customHeight="1"/>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>十、請 AI 填寫時的提醒</t>
         </is>
       </c>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="7" t="n"/>
-    </row>
-    <row r="87" ht="25.5" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>先決定 offset，再依 offset 寫文案與回饋，避免數值和文字對不上</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>遵守第七節的階段濕度規則</t>
-        </is>
-      </c>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
     </row>
     <row r="89" ht="25.5" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>文案不出現數字，只用敘事暗示；選項文案（choice_a/b/c_desc）不可超過 14 字（含標點），事件敘述與回饋不限字數</t>
+          <t>先決定 offset，再依 offset 寫文案與回饋，避免數值和文字對不上</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>遵守第七節的階段濕度規則</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>文案不出現數字，只用敘事暗示；選項文案（choice_a/b/c_desc）不可超過 14 字（含標點），事件敘述與回饋不限字數</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>填完後對照本頁規則逐格檢查</t>
         </is>

--- a/Doc/FGJ 2026表格_v2.xlsx
+++ b/Doc/FGJ 2026表格_v2.xlsx
@@ -3,15 +3,20 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="event_list" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="title_list" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="想法" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="格式說明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="插圖需求" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="人物列表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="想法" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="格式說明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'插圖需求'!$A$4:$E$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人物列表'!$A$3:$G$45</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -89,6 +94,22 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -125,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,6 +176,21 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -420,6 +456,18 @@
 （詳見「格式說明」分頁）</t>
       </text>
     </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>結局畫面顯示的敘事文字（不限字數）
+（詳見「格式說明」分頁）</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>給玩家／企劃看的條件說明，需與 reach_* 或觸發選項的需求一致
+（詳見「格式說明」分頁）</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -629,18 +677,18 @@
   <dimension ref="A1:W43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" style="29" min="1" max="1"/>
+    <col width="16" customWidth="1" style="29" min="2" max="2"/>
+    <col width="40" customWidth="1" style="29" min="3" max="3"/>
+    <col width="28" customWidth="1" style="29" min="4" max="4"/>
+    <col width="16" customWidth="1" style="29" min="5" max="5"/>
+    <col width="13" customWidth="1" style="29" min="6" max="9"/>
+    <col width="16" customWidth="1" style="29" min="10" max="10"/>
+    <col width="13" customWidth="1" style="29" min="11" max="15"/>
+    <col width="16" customWidth="1" style="29" min="16" max="16"/>
+    <col width="13" customWidth="1" style="29" min="17" max="21"/>
+    <col width="16" customWidth="1" style="29" min="22" max="22"/>
+    <col width="13" customWidth="1" style="29" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -986,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="51" customHeight="1" s="29">
       <c r="A4" s="3" t="n">
         <v>1001</v>
       </c>
@@ -1075,7 +1123,7 @@
       </c>
       <c r="W4" s="3" t="n"/>
     </row>
-    <row r="5" ht="63.75" customHeight="1">
+    <row r="5" ht="63.75" customHeight="1" s="29">
       <c r="A5" s="3" t="n">
         <v>1002</v>
       </c>
@@ -1164,7 +1212,7 @@
       </c>
       <c r="W5" s="3" t="n"/>
     </row>
-    <row r="6" ht="38.25" customHeight="1">
+    <row r="6" ht="38.25" customHeight="1" s="29">
       <c r="A6" s="3" t="n">
         <v>1003</v>
       </c>
@@ -1253,7 +1301,7 @@
       </c>
       <c r="W6" s="3" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="51" customHeight="1" s="29">
       <c r="A7" s="3" t="n">
         <v>1004</v>
       </c>
@@ -1342,7 +1390,7 @@
       </c>
       <c r="W7" s="3" t="n"/>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="51" customHeight="1" s="29">
       <c r="A8" s="3" t="n">
         <v>1005</v>
       </c>
@@ -1431,7 +1479,7 @@
       </c>
       <c r="W8" s="3" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="51" customHeight="1" s="29">
       <c r="A9" s="3" t="n">
         <v>1006</v>
       </c>
@@ -1520,7 +1568,7 @@
       </c>
       <c r="W9" s="3" t="n"/>
     </row>
-    <row r="10" ht="63.75" customHeight="1">
+    <row r="10" ht="63.75" customHeight="1" s="29">
       <c r="A10" s="3" t="n">
         <v>1007</v>
       </c>
@@ -1534,7 +1582,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>一個浪子獨自在空地上踢球，一腳把球踢到你面前。</t>
+          <t>一顆足球滾了過來，後面跟著一群大叫的小朋友。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1555,7 +1603,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>球從你頭上飛過，浪子追球時踩了你好幾腳，但你還站得起來。</t>
+          <t>球從你頭上飛過，小朋友追球時踩了你好幾腳，但你還站得起來。</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1566,7 +1614,7 @@
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>把球頂回去</t>
+          <t>使出浪子踢球</t>
         </is>
       </c>
       <c r="M10" s="4" t="n"/>
@@ -1577,7 +1625,7 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>浪子愣了一下，笑著說：「欸，你這株草很會踢喔。」</t>
+          <t>你一腳把球踢回去，弧線漂亮得不像話。小朋友歡呼：「那株草好會踢！」</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -1599,7 +1647,7 @@
       </c>
       <c r="U10" s="10" t="inlineStr">
         <is>
-          <t>跑道燙得冒煙，浪子在後面喊你回來踢球，你頭也不回。</t>
+          <t>跑道燙得冒煙，你跑得飛快，葉子也快烤焦了。</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -1609,7 +1657,7 @@
       </c>
       <c r="W10" s="3" t="n"/>
     </row>
-    <row r="11" ht="51" customHeight="1">
+    <row r="11" ht="51" customHeight="1" s="29">
       <c r="A11" s="3" t="n">
         <v>1008</v>
       </c>
@@ -1698,7 +1746,7 @@
       </c>
       <c r="W11" s="3" t="n"/>
     </row>
-    <row r="12" ht="51" customHeight="1">
+    <row r="12" ht="51" customHeight="1" s="29">
       <c r="A12" s="3" t="n">
         <v>1009</v>
       </c>
@@ -1787,7 +1835,7 @@
       </c>
       <c r="W12" s="3" t="n"/>
     </row>
-    <row r="13" ht="38.25" customHeight="1">
+    <row r="13" ht="38.25" customHeight="1" s="29">
       <c r="A13" s="3" t="n">
         <v>1010</v>
       </c>
@@ -1876,7 +1924,7 @@
       </c>
       <c r="W13" s="3" t="n"/>
     </row>
-    <row r="14" ht="51" customHeight="1">
+    <row r="14" ht="51" customHeight="1" s="29">
       <c r="A14" s="3" t="n">
         <v>2001</v>
       </c>
@@ -1969,7 +2017,7 @@
       </c>
       <c r="W14" s="3" t="n"/>
     </row>
-    <row r="15" ht="51" customHeight="1">
+    <row r="15" ht="51" customHeight="1" s="29">
       <c r="A15" s="3" t="n">
         <v>2002</v>
       </c>
@@ -2066,7 +2114,7 @@
       </c>
       <c r="W15" s="3" t="n"/>
     </row>
-    <row r="16" ht="51" customHeight="1">
+    <row r="16" ht="51" customHeight="1" s="29">
       <c r="A16" s="3" t="n">
         <v>2003</v>
       </c>
@@ -2159,7 +2207,7 @@
       </c>
       <c r="W16" s="3" t="n"/>
     </row>
-    <row r="17" ht="89.25" customHeight="1">
+    <row r="17" ht="89.25" customHeight="1" s="29">
       <c r="A17" s="3" t="n">
         <v>2004</v>
       </c>
@@ -2173,7 +2221,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>公路邊，那個浪子又在踢球，一腳把球踢到了馬路對面。</t>
+          <t>公路對面的小朋友一不小心，把足球踢到了車來車往的馬路中央。</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2194,7 +2242,7 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>綠燈亮了，你和浪子一起抬頭挺胸走過斑馬線。</t>
+          <t>綠燈亮了，你抬頭挺胸走過斑馬線，順手把球推回給小朋友。</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2205,7 +2253,7 @@
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>趁空檔衝去撿球</t>
+          <t>衝上馬路使出浪子踢球</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -2220,7 +2268,7 @@
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>你像一道綠色閃電，搶先撿到了球。浪子吹了聲口哨，柏油路的熱氣卻燙得你發暈。</t>
+          <t>你衝到馬路中央，一記浪子踢球把球送回對面。小朋友看傻了眼，柏油路的熱氣卻燙得你發暈。</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -2242,7 +2290,7 @@
       </c>
       <c r="U17" s="10" t="inlineStr">
         <is>
-          <t>每一步都很燙，你咬牙爬到對面時，浪子早就踢著球走遠了。</t>
+          <t>每一步都很燙，你咬牙爬到了對面。</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
@@ -2252,7 +2300,7 @@
       </c>
       <c r="W17" s="3" t="n"/>
     </row>
-    <row r="18" ht="51" customHeight="1">
+    <row r="18" ht="51" customHeight="1" s="29">
       <c r="A18" s="3" t="n">
         <v>2005</v>
       </c>
@@ -2349,7 +2397,7 @@
       </c>
       <c r="W18" s="3" t="n"/>
     </row>
-    <row r="19" ht="51" customHeight="1">
+    <row r="19" ht="51" customHeight="1" s="29">
       <c r="A19" s="3" t="n">
         <v>2006</v>
       </c>
@@ -2438,7 +2486,7 @@
       </c>
       <c r="W19" s="3" t="n"/>
     </row>
-    <row r="20" ht="51" customHeight="1">
+    <row r="20" ht="51" customHeight="1" s="29">
       <c r="A20" s="3" t="n">
         <v>2007</v>
       </c>
@@ -2531,7 +2579,7 @@
       </c>
       <c r="W20" s="3" t="n"/>
     </row>
-    <row r="21" ht="63.75" customHeight="1">
+    <row r="21" ht="63.75" customHeight="1" s="29">
       <c r="A21" s="3" t="n">
         <v>2008</v>
       </c>
@@ -2622,7 +2670,7 @@
       </c>
       <c r="W21" s="3" t="n"/>
     </row>
-    <row r="22" ht="63.75" customHeight="1">
+    <row r="22" ht="63.75" customHeight="1" s="29">
       <c r="A22" s="3" t="n">
         <v>2009</v>
       </c>
@@ -2713,7 +2761,7 @@
       </c>
       <c r="W22" s="3" t="n"/>
     </row>
-    <row r="23" ht="51" customHeight="1">
+    <row r="23" ht="51" customHeight="1" s="29">
       <c r="A23" s="3" t="n">
         <v>2010</v>
       </c>
@@ -2804,7 +2852,7 @@
       </c>
       <c r="W23" s="3" t="n"/>
     </row>
-    <row r="24" ht="38.25" customHeight="1">
+    <row r="24" ht="38.25" customHeight="1" s="29">
       <c r="A24" s="3" t="n">
         <v>3001</v>
       </c>
@@ -2901,7 +2949,7 @@
       </c>
       <c r="W24" s="3" t="n"/>
     </row>
-    <row r="25" ht="63.75" customHeight="1">
+    <row r="25" ht="63.75" customHeight="1" s="29">
       <c r="A25" s="3" t="n">
         <v>3002</v>
       </c>
@@ -2998,7 +3046,7 @@
       </c>
       <c r="W25" s="3" t="n"/>
     </row>
-    <row r="26" ht="51" customHeight="1">
+    <row r="26" ht="51" customHeight="1" s="29">
       <c r="A26" s="3" t="n">
         <v>3003</v>
       </c>
@@ -3091,7 +3139,7 @@
       </c>
       <c r="W26" s="3" t="n"/>
     </row>
-    <row r="27" ht="51" customHeight="1">
+    <row r="27" ht="51" customHeight="1" s="29">
       <c r="A27" s="3" t="n">
         <v>3004</v>
       </c>
@@ -3188,7 +3236,7 @@
       </c>
       <c r="W27" s="3" t="n"/>
     </row>
-    <row r="28" ht="38.25" customHeight="1">
+    <row r="28" ht="38.25" customHeight="1" s="29">
       <c r="A28" s="3" t="n">
         <v>3005</v>
       </c>
@@ -3281,7 +3329,7 @@
       </c>
       <c r="W28" s="3" t="n"/>
     </row>
-    <row r="29" ht="51" customHeight="1">
+    <row r="29" ht="51" customHeight="1" s="29">
       <c r="A29" s="3" t="n">
         <v>3006</v>
       </c>
@@ -3374,7 +3422,7 @@
       </c>
       <c r="W29" s="3" t="n"/>
     </row>
-    <row r="30" ht="63.75" customHeight="1">
+    <row r="30" ht="63.75" customHeight="1" s="29">
       <c r="A30" s="3" t="n">
         <v>3007</v>
       </c>
@@ -3471,7 +3519,7 @@
       </c>
       <c r="W30" s="3" t="n"/>
     </row>
-    <row r="31" ht="38.25" customHeight="1">
+    <row r="31" ht="38.25" customHeight="1" s="29">
       <c r="A31" s="3" t="n">
         <v>3008</v>
       </c>
@@ -3568,7 +3616,7 @@
       </c>
       <c r="W31" s="3" t="n"/>
     </row>
-    <row r="32" ht="51" customHeight="1">
+    <row r="32" ht="51" customHeight="1" s="29">
       <c r="A32" s="3" t="n">
         <v>3009</v>
       </c>
@@ -3665,7 +3713,7 @@
       </c>
       <c r="W32" s="3" t="n"/>
     </row>
-    <row r="33" ht="38.25" customHeight="1">
+    <row r="33" ht="38.25" customHeight="1" s="29">
       <c r="A33" s="3" t="n">
         <v>3010</v>
       </c>
@@ -3762,7 +3810,7 @@
       </c>
       <c r="W33" s="3" t="n"/>
     </row>
-    <row r="34" ht="63.75" customHeight="1">
+    <row r="34" ht="63.75" customHeight="1" s="29">
       <c r="A34" s="3" t="n">
         <v>3011</v>
       </c>
@@ -3855,7 +3903,7 @@
       </c>
       <c r="W34" s="3" t="n"/>
     </row>
-    <row r="35" ht="38.25" customHeight="1">
+    <row r="35" ht="38.25" customHeight="1" s="29">
       <c r="A35" s="3" t="n">
         <v>3012</v>
       </c>
@@ -3948,7 +3996,7 @@
       </c>
       <c r="W35" s="3" t="n"/>
     </row>
-    <row r="36" ht="38.25" customHeight="1">
+    <row r="36" ht="38.25" customHeight="1" s="29">
       <c r="A36" s="3" t="n">
         <v>3013</v>
       </c>
@@ -4041,7 +4089,7 @@
       </c>
       <c r="W36" s="3" t="n"/>
     </row>
-    <row r="37" ht="51" customHeight="1">
+    <row r="37" ht="51" customHeight="1" s="29">
       <c r="A37" s="3" t="n">
         <v>3014</v>
       </c>
@@ -4138,7 +4186,7 @@
       </c>
       <c r="W37" s="3" t="n"/>
     </row>
-    <row r="38" ht="51" customHeight="1">
+    <row r="38" ht="51" customHeight="1" s="29">
       <c r="A38" s="3" t="n">
         <v>3015</v>
       </c>
@@ -4229,7 +4277,7 @@
       </c>
       <c r="W38" s="3" t="n"/>
     </row>
-    <row r="39" ht="51" customHeight="1">
+    <row r="39" ht="51" customHeight="1" s="29">
       <c r="A39" s="3" t="n">
         <v>3016</v>
       </c>
@@ -4320,7 +4368,7 @@
       </c>
       <c r="W39" s="3" t="n"/>
     </row>
-    <row r="40" ht="51" customHeight="1">
+    <row r="40" ht="51" customHeight="1" s="29">
       <c r="A40" s="3" t="n">
         <v>3017</v>
       </c>
@@ -4411,7 +4459,7 @@
       </c>
       <c r="W40" s="3" t="n"/>
     </row>
-    <row r="41" ht="51" customHeight="1">
+    <row r="41" ht="51" customHeight="1" s="29">
       <c r="A41" s="3" t="n">
         <v>3018</v>
       </c>
@@ -4498,7 +4546,7 @@
       </c>
       <c r="W41" s="3" t="n"/>
     </row>
-    <row r="42" ht="51" customHeight="1">
+    <row r="42" ht="51" customHeight="1" s="29">
       <c r="A42" s="3" t="n">
         <v>3019</v>
       </c>
@@ -4593,7 +4641,7 @@
       </c>
       <c r="W42" s="3" t="n"/>
     </row>
-    <row r="43" ht="38.25" customHeight="1">
+    <row r="43" ht="38.25" customHeight="1" s="29">
       <c r="A43" s="3" t="n">
         <v>3020</v>
       </c>
@@ -4696,14 +4744,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" style="29" min="1" max="1"/>
+    <col width="18" customWidth="1" style="29" min="2" max="2"/>
+    <col width="14" customWidth="1" style="29" min="3" max="3"/>
+    <col width="12" customWidth="1" style="29" min="4" max="6"/>
+    <col width="46" customWidth="1" style="29" min="7" max="7"/>
+    <col width="46" customWidth="1" style="29" min="8" max="8"/>
+    <col width="20" customWidth="1" style="29" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4739,6 +4789,16 @@
       </c>
       <c r="G1" s="11" t="inlineStr">
         <is>
+          <t>結局描述</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>達成條件</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
@@ -4774,7 +4834,17 @@
           <t>reach_tgh</t>
         </is>
       </c>
-      <c r="G2" s="11" t="n"/>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>title_desc</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>title_condition</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -4807,7 +4877,17 @@
           <t>string</t>
         </is>
       </c>
-      <c r="G3" s="11" t="n"/>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -4823,13 +4903,23 @@
           <t>title_0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>你什麼都沒有特別去爭，也什麼都沒有失去。風吹過時你輕輕搖擺，安安靜靜地當一株草，這也是一種活法。</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值介於 -9 ～ 9（中立）、速度 &lt; 15、韌度 &lt; 15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>全部未達標（無為的草）</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
+    <row r="5" ht="13.5" customHeight="1" s="29">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -4848,8 +4938,18 @@
           <t>spd&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>你把青蛙教的閃身步練到出神入化，沒有任何東西碰得到你。大家只記得一道綠色殘影，從草原一路閃進了城市。</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值介於 -9 ～ 9（中立）、速度 ≥ 15、韌度 &lt; 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1" s="29">
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
@@ -4868,8 +4968,18 @@
           <t>tgh&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>風吹不倒、日曬不枯，連講話石頭都說你比它還硬。你的根深深扎進土裡，再也沒有什麼能把你拔起來。</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值介於 -9 ～ 9（中立）、速度 &lt; 15、韌度 ≥ 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1" s="29">
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
@@ -4893,8 +5003,18 @@
           <t>tgh&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>跑得快、扛得住，你成了草原上傳說中的那株草。不管遇到什麼，你都能撐過去，然後繼續往前跑。</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值介於 -9 ～ 9（中立）、速度 ≥ 15、韌度 ≥ 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1" s="29">
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
@@ -4913,8 +5033,18 @@
           <t>mor&gt;=10</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>一路上你幫了好多小動物，螞蟻、瓢蟲和蝸牛都記得你。你也許不是最快、最強的草，卻是大家最喜歡的那一株。</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≥ 10、速度 &lt; 15、韌度 &lt; 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1" s="29">
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
@@ -4938,8 +5068,18 @@
           <t>spd&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>哪裡有人需要幫忙，你就第一個衝到哪裡。跑得又快、心又暖，你成了大家口中的綠色快遞員。</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≥ 10、速度 ≥ 15、韌度 &lt; 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1" s="29">
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
@@ -4963,8 +5103,18 @@
           <t>tgh&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>你用自己的身體替小生命擋風遮沙，從來不曾退縮。在你身後，總有一群被你保護著的小傢伙。</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≥ 10、速度 &lt; 15、韌度 ≥ 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1" s="29">
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
@@ -4993,8 +5143,18 @@
           <t>tgh&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>又快、又強、又善良，你完美得不像一株草。據說你經過的地方，枯萎的花都會重新抬起頭來。</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≥ 10、速度 ≥ 15、韌度 ≥ 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="13.5" customHeight="1" s="29">
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
@@ -5013,8 +5173,18 @@
           <t>mor&lt;=-10</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>你偷、你騙、你把別人推出去擋災，小動物見到你都繞道走。不過說實話，你活得挺開心的。</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≤ -10、速度 &lt; 15、韌度 &lt; 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1" s="29">
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
@@ -5038,8 +5208,18 @@
           <t>spd&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>偷完就跑，從來沒有人追得上你。整條路上都流傳著一株綠色小賊的傳說。</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≤ -10、速度 ≥ 15、韌度 &lt; 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1" s="29">
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
@@ -5063,8 +5243,18 @@
           <t>tgh&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1">
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>你又硬又壞，擋在面前的東西全被你踢開。大家都怕你，而你一點也不在乎。</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≤ -10、速度 &lt; 15、韌度 ≥ 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1" s="29">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -5093,8 +5283,18 @@
           <t>tgh&gt;=15</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="13.5" customHeight="1">
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>跑得最快、站得最穩、心也最黑，你成了草界聞風喪膽的大魔王。小動物們一聽到你的名字就發抖。</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>沒有觸發特殊結局，且結算時：善良值 ≤ -10、速度 ≥ 15、韌度 ≥ 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="13.5" customHeight="1" s="29">
       <c r="A16" s="5" t="n">
         <v>2008</v>
       </c>
@@ -5108,13 +5308,23 @@
           <t>title_2008</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>你被學生小心地夾進標本簿，貼上「新品種」的標籤。從此你永遠保持著最帥的姿勢，在自然教室裡供大家欣賞。</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 2008 選擇 A「擺出最帥的姿勢」（無需求）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" ht="13.5" customHeight="1" s="29">
       <c r="A17" s="5" t="n">
         <v>2009</v>
       </c>
@@ -5128,7 +5338,17 @@
           <t>title_2009</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>你熱情地跟兔子打招呼，兔子也熱情地……吃掉了你。至少，你讓一隻兔子度過了美好的一餐。</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 2009 選擇 A「主動湊過去打招呼」（無需求）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -5148,13 +5368,23 @@
           <t>title_2010</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>小女孩把你帶回家，插在窗台的小花瓶裡。每天早上她都幫你換水，你在陽光下過著再也不用奔跑的日子。</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 2010 選擇 A「用力挺直身體讓她看見」（需 善良值 ≥ 10）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
+    <row r="19" ht="13.5" customHeight="1" s="29">
       <c r="A19" s="5" t="n">
         <v>3015</v>
       </c>
@@ -5168,13 +5398,23 @@
           <t>title_3015</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>你跳上會飛的胡蘿蔔，飛過雲層、飛向月亮。地上的人只看到夜空中多了一個綠色的小點，從此你再也沒有回來。</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 3015 選擇 A「跳上胡蘿蔔」（需 速度 ≥ 20）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
+    <row r="20" ht="13.5" customHeight="1" s="29">
       <c r="A20" s="5" t="n">
         <v>3016</v>
       </c>
@@ -5188,13 +5428,23 @@
           <t>title_3016</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>你鑽進柏油路的裂縫，在城市裡扎下了根。車子來來去去，你始終在那裡，成了城市裡最頑強的那株草。</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 3016 選擇 A「鑽進裂縫住下來」（需 韌度 ≥ 20）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
+    <row r="21" ht="13.5" customHeight="1" s="29">
       <c r="A21" s="5" t="n">
         <v>3017</v>
       </c>
@@ -5208,13 +5458,23 @@
           <t>title_3017</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>你在無邊無際的荒地正中央扎根，開出了第一朵小花。也許有一天，這片荒地會因為你變成一片草原。</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 3017 選擇 A「就在這裡扎根」（需 善良值 ≥ 10）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
+    <row r="22" ht="13.5" customHeight="1" s="29">
       <c r="A22" s="5" t="n">
         <v>3018</v>
       </c>
@@ -5228,13 +5488,23 @@
           <t>title_3018</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>你跳進爺爺的竹籃，被煮成了一壺消暑的青草茶。喝過的人都說好喝，爺爺也笑得合不攏嘴。</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 3018 選擇 A「跳進竹籃」（無需求）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
+    <row r="23" ht="13.5" customHeight="1" s="29">
       <c r="A23" s="5" t="n">
         <v>3019</v>
       </c>
@@ -5248,13 +5518,23 @@
           <t>title_3019</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
+        <is>
+          <t>老師傅把你編成一隻草蜢，掛在小孩的書包上。你跟著小孩上學、放學，用另一種方式繼續旅行。</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 3019 選擇 A「自願當材料」（需 韌度 ≥ 15）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" ht="13.5" customHeight="1" s="29">
       <c r="A24" s="5" t="n">
         <v>3020</v>
       </c>
@@ -5268,7 +5548,17 @@
           <t>title_3020</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>你衝進海浪裡，變成了一株會游泳的海草。陸地上的旅程結束了，海裡的冒險才正要開始。</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="inlineStr">
+        <is>
+          <t>【特殊結局】在事件 3020 選擇 A「衝向大海」（需 速度 ≥ 25）。觸發後立即結束，優先於屬性稱號</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
@@ -5278,23 +5568,30 @@
       <c r="A25" s="5" t="n">
         <v>3021</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>特殊結局（備用）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="14" t="n"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="14" t="n"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="14" t="n"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="14" t="n"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32" ht="13.5" customHeight="1" s="29">
+      <c r="K32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="13.5" customHeight="1" s="29">
+      <c r="K33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="13.5" customHeight="1" s="29">
+      <c r="K34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="13.5" customHeight="1" s="29">
+      <c r="K35" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5305,209 +5602,4080 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:E164"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="14.42578125" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" style="29" min="1" max="1"/>
+    <col width="79.140625" customWidth="1" style="29" min="2" max="2"/>
+    <col width="20" customWidth="1" style="29" min="3" max="3"/>
+    <col width="18" customWidth="1" style="29" min="4" max="4"/>
+    <col width="9" customWidth="1" style="29" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>共通風格</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>每張圖的提詞前面都加上這段：橫向 16:9 畫面，Q 版可愛手繪風，主角是一株有小腳、有表情的擬人化綠色小草，明亮溫暖的色調，畫面中不放文字。（風格可依美術定案調整）</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>初始濕度</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>准許濕度</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>0~100</t>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>圖片由 Codex image generate 產生。事件圖＝事件發生前的場景；選項結果圖＝選完該選項後的結果。「出場人物」不含主角小草（每張圖都有小草）。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Demo 5輪</t>
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>提詞</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>出場人物</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>檔名</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>事件ID</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>實際 15輪結束</t>
-        </is>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>清晨的草原上，一顆圓滾滾的露珠掛在蒲公英葉尖搖搖欲墜，小草站在下方抬頭看。</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>蒲公英</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>event_1001</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>一列螞蟻扛著餅乾屑排成長隊，擋在小草面前的小路上。</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>螞蟻</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>event_1002</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>雨後的地面上有一個小水窪，倒映著藍天白雲，小草站在水邊。</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>event_1003</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>1003</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Demo版濕度選項</t>
-        </is>
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>一頭大牛低頭吃草，一路朝小草這邊吃過來。</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>牛</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>event_1004</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>1004</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>一個-20</t>
-        </is>
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>路邊一顆有臉的石頭開口說話，遠方的天空捲起大風。</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>event_1005</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>1005</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>一個-20</t>
-        </is>
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>一隻慢吞吞的蝸牛抬頭，問小草哪裡有水。</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>蝸牛</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>event_1006</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>1006</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>一個-20</t>
-        </is>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>一顆足球滾向小草，後面跟著一群大叫的小朋友。</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>event_1007</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>1007</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>兩個-20</t>
-        </is>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>一隻蚯蚓從土裡探出頭，周圍的土被翻得鬆鬆軟軟。</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>蚯蚓</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>event_1008</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>1008</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>兩個-20</t>
-        </is>
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>一隻青蛙坐在荷葉上擺出師父的架勢，要教小草閃身步。</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>event_1009</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>兩個-20</t>
-        </is>
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>草地上的灑水器轉呀轉，噴出一圈圈水花。</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>event_1010</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>1010</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>農夫扛著鋤頭走進菜田準備除草，小草躲在田邊。</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>農夫</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>event_2001</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>2001</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>一條灌溉水渠嘩啦啦地流過田邊，小草站在渠邊。</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>event_2002</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>2002</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>田中央站著戴斗笠的稻草人，斗笠下有一小片陰影。</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>稻草人</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>event_2003</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>2003</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>車來車往的公路上，一顆足球停在馬路中央，對面的小朋友著急地看著。</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>event_2004</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>2004</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>一根拍著葉子飛行的胡蘿蔔從頭上飛過，後面追著一群兔子。</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔、兔子</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>event_2005</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>2005</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>一隻牧羊犬趕著羊群經過，轉頭看了小草一眼。</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>牧羊犬、羊</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>event_2006</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>2006</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>稻田邊，青蛙師父雙手抱胸，要考小草的閃身步。</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>event_2007</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>2007</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>戴眼鏡的學生拿著放大鏡蹲在小草面前，眼睛閃閃發亮。</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>戴眼鏡的學生</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>event_2008</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="n">
+        <v>2008</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>三個-10</t>
-        </is>
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>一隻兔子抽動著鼻子，蹦蹦跳跳地靠近小草。</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>event_2009</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>小女孩蹲在路邊，認真挑選要帶回家的花草。</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>小女孩</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>event_2010</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>沙漠邊緣，一陣夾帶沙子的熱風撲向小草。</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>event_3001</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>一株老仙人掌孤零零地站在沙地上，刺像白鬍子一樣。</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>仙人掌</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>event_3002</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="n">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>城市街道上，路邊有一條排水溝，小草站在人行道上。</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>event_3003</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>冷氣室外機轟轟作響，噴出扭曲的熱風。</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>event_3004</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>一隻流浪貓懶洋洋地躺在牆角。</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>流浪貓</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>event_3005</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭滾到小草面前，氣喘吁吁地打招呼。</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>event_3006</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>廣場上一群鴿子正在搶食麵包屑。</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>鴿子</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>event_3007</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="n">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>一望無際的停車場，地面冒著熱氣。</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>event_3008</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>工地裡剛鋪好的水泥還沒乾，旁邊立著告示牌。</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>event_3009</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>遠方颳來巨大的沙塵暴，天色一下子變暗。</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>event_3010</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>熱鬧的台灣夜市，攤位冒著油煙、擠滿人潮。</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>攤販、夜市人潮</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>event_3011</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>小草站在一排鐵皮屋頂上，俯瞰整座城市。</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>event_3012</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="n">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>海邊白花花的鹽田，招潮蟹在一旁揮著大螯。</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
+        <is>
+          <t>招潮蟹</t>
+        </is>
+      </c>
+      <c r="D37" s="28" t="inlineStr">
+        <is>
+          <t>event_3013</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="n">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>一株老蒲公英頂著最後一圈白絨毛，在熱風裡發抖。</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>老蒲公英</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>event_3014</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="n">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔降落在小草面前，邀請它一起飛去月亮。</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="inlineStr">
+        <is>
+          <t>event_3015</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>柏油路上有一道小小的裂縫，裡面有一點點土。</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="inlineStr">
+        <is>
+          <t>event_3016</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>一片無邊無際的寂靜荒地，風停了，小草站在正中央。</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="inlineStr">
+        <is>
+          <t>event_3017</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="inlineStr">
+        <is>
+          <t>一位爺爺提著竹籃，在路邊採青草。</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="inlineStr">
+        <is>
+          <t>爺爺</t>
+        </is>
+      </c>
+      <c r="D42" s="28" t="inlineStr">
+        <is>
+          <t>event_3018</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="inlineStr">
+        <is>
+          <t>樹下的老師傅正用草葉編東西，手指靈巧得像在變魔術。</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>老師傅</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr">
+        <is>
+          <t>event_3019</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="n">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>事件（事前）</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>沙灘上傳來海浪聲，小草望向遠方的大海。</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr">
+        <is>
+          <t>event_3020</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="inlineStr">
+        <is>
+          <t>小草擺著最帥的姿勢被夾在標本簿裡，旁邊貼著標籤。</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D45" s="28" t="inlineStr">
+        <is>
+          <t>event_2008_a</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="n">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="inlineStr">
+        <is>
+          <t>小草熱情地湊過去打招呼，兔子圍好餐巾、眼睛發亮地看著它（逗趣、不血腥）。</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>event_2009_a</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="inlineStr">
+        <is>
+          <t>小草插在窗台的小花瓶裡，陽光灑進來，小女孩正在幫它換水。</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>小女孩</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="inlineStr">
+        <is>
+          <t>event_2010_a</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>小草騎著胡蘿蔔飛過雲層，朝巨大的月亮前進。</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>event_3015_a</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>小草在柏油裂縫裡扎根挺立，車輪在旁邊來來去去。</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>event_3016_a</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="inlineStr">
+        <is>
+          <t>小草在荒地正中央扎根，頭頂開出第一朵小花。</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>event_3017_a</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>一壺冒著熱氣的青草茶，小草的葉子漂在茶裡，爺爺端著茶杯一臉消暑。</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>爺爺</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>event_3018_a</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="n">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>小草被編成一隻草蜢，掛在小孩的書包上一起旅行。</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>小孩</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>event_3019_a</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="n">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>特殊結局</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>小草跳進浪裡變成會游泳的海草，在海中快樂地游動。</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="inlineStr">
+        <is>
+          <t>event_3020_a</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>小草張開葉子接住露珠，水珠滑進根部，整株閃閃發亮、精神飽滿。</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="inlineStr">
+        <is>
+          <t>event_1001_a</t>
+        </is>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>小草推動葉尖的露珠，讓它滴給口渴的蒲公英，蒲公英開心地點頭。</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>蒲公英</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="inlineStr">
+        <is>
+          <t>event_1001_b</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>太陽剛升起，小草在草原上飛奔，葉尖微微捲起。</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="inlineStr">
+        <is>
+          <t>event_1001_c</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>小草挺直站在路邊耐心等待，螞蟻隊伍從腳邊慢慢走過，根牢牢抓著地面。</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
+        <is>
+          <t>螞蟻</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="inlineStr">
+        <is>
+          <t>event_1002_a</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>小草抱著一塊餅乾屑偷笑著逃走，後面的螞蟻揮拳生氣。</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
+        <is>
+          <t>螞蟻</t>
+        </is>
+      </c>
+      <c r="D58" s="28" t="inlineStr">
+        <is>
+          <t>event_1002_b</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>小草在曬得發燙、冒著熱氣的石頭上跳腳。</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D59" s="28" t="inlineStr">
+        <is>
+          <t>event_1002_c</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>小草整株泡在水窪裡一臉陶醉，雙腳泡得軟趴趴的。</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D60" s="28" t="inlineStr">
+        <is>
+          <t>event_1003_a</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>幾隻瓢蟲排隊在水窪邊喝水，還對著小草唱歌。</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>瓢蟲</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="inlineStr">
+        <is>
+          <t>event_1003_b</t>
+        </is>
+      </c>
+      <c r="E61" s="28" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>小草帥氣地躍過水窪，落地處正好在刺眼的大太陽底下。</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="inlineStr">
+        <is>
+          <t>event_1003_c</t>
+        </is>
+      </c>
+      <c r="E62" s="28" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>小草躲在一坨牛糞後面，捏著鼻子一臉嫌棄，牛從旁邊經過。</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>牛</t>
+        </is>
+      </c>
+      <c r="D63" s="28" t="inlineStr">
+        <is>
+          <t>event_1004_a</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>小草把旁邊另一株小草推向牛嘴，自己偷偷溜走。</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>牛、另一株小草</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="inlineStr">
+        <is>
+          <t>event_1004_b</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>小草在乾枯的牧草地上全力奔跑，身後揚起塵土。</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D65" s="28" t="inlineStr">
+        <is>
+          <t>event_1004_c</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>大風吹過，小草緊緊抓住地面，旁邊的石頭得意地說「看吧」。</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="inlineStr">
+        <is>
+          <t>event_1005_a</t>
+        </is>
+      </c>
+      <c r="E66" s="28" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B67" s="28" t="inlineStr">
+        <is>
+          <t>小草乘著大風滑行，一下子跑得好遠，石頭在後方呼喊。</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="inlineStr">
+        <is>
+          <t>event_1005_b</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B68" s="28" t="inlineStr">
+        <is>
+          <t>小草迎著強風站得筆直，葉子被吹得乾巴巴，石頭在一旁搖頭。</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D68" s="28" t="inlineStr">
+        <is>
+          <t>event_1005_c</t>
+        </is>
+      </c>
+      <c r="E68" s="28" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B69" s="28" t="inlineStr">
+        <is>
+          <t>小草和蝸牛並肩在小溪邊開心地喝水。</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>蝸牛</t>
+        </is>
+      </c>
+      <c r="D69" s="28" t="inlineStr">
+        <is>
+          <t>event_1006_a</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="inlineStr">
+        <is>
+          <t>小草指向錯誤的方向偷笑，蝸牛慢慢爬向遠方的乾地。</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>蝸牛</t>
+        </is>
+      </c>
+      <c r="D70" s="28" t="inlineStr">
+        <is>
+          <t>event_1006_b</t>
+        </is>
+      </c>
+      <c r="E70" s="28" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="inlineStr">
+        <is>
+          <t>小草頂著大太陽趕路，蝸牛被留在後方。</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>蝸牛</t>
+        </is>
+      </c>
+      <c r="D71" s="28" t="inlineStr">
+        <is>
+          <t>event_1006_c</t>
+        </is>
+      </c>
+      <c r="E71" s="28" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t>小草趴在地上裝死，球從頭上飛過，小朋友的鞋子踩在旁邊。</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="D72" s="28" t="inlineStr">
+        <is>
+          <t>event_1007_a</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B73" s="28" t="inlineStr">
+        <is>
+          <t>小草使出招式「浪子踢球」，把球踢出漂亮的弧線，小朋友在後方歡呼。</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="inlineStr">
+        <is>
+          <t>event_1007_b</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B74" s="28" t="inlineStr">
+        <is>
+          <t>小草在冒煙的操場跑道上狂奔，葉尖被曬得捲起。</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr">
+        <is>
+          <t>event_1007_c</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="inlineStr">
+        <is>
+          <t>小草鑽進濕軟的泥土裡只露出葉子，一臉安心。</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>蚯蚓</t>
+        </is>
+      </c>
+      <c r="D75" s="28" t="inlineStr">
+        <is>
+          <t>event_1008_a</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B76" s="28" t="inlineStr">
+        <is>
+          <t>小草踩著蚯蚓的頭高高跳起，蚯蚓在下面抱著頭。</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>蚯蚓</t>
+        </is>
+      </c>
+      <c r="D76" s="28" t="inlineStr">
+        <is>
+          <t>event_1008_b</t>
+        </is>
+      </c>
+      <c r="E76" s="28" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B77" s="28" t="inlineStr">
+        <is>
+          <t>小草站在土堆頂端曬太陽，莖被曬得硬梆梆。</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D77" s="28" t="inlineStr">
+        <is>
+          <t>event_1008_c</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="inlineStr">
+        <is>
+          <t>小草左右快速閃動練習閃身步，留下殘影，青蛙在旁指導。</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D78" s="28" t="inlineStr">
+        <is>
+          <t>event_1009_a</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B79" s="28" t="inlineStr">
+        <is>
+          <t>小草幫青蛙抓蚊子，青蛙開心地甩了小草一身水珠。</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D79" s="28" t="inlineStr">
+        <is>
+          <t>event_1009_b</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="inlineStr">
+        <is>
+          <t>小草跑向乾燥的地面，青蛙在荷葉上對著它大喊。</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D80" s="28" t="inlineStr">
+        <is>
+          <t>event_1009_c</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B81" s="28" t="inlineStr">
+        <is>
+          <t>小草在灑水器的水花中開心洗澡，整株濕透透。</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D81" s="28" t="inlineStr">
+        <is>
+          <t>event_1010_a</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B82" s="28" t="inlineStr">
+        <is>
+          <t>小草把灑水器轉向枯萎的花圃，花朵慢慢抬起頭道謝。</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>花圃的花</t>
+        </is>
+      </c>
+      <c r="D82" s="28" t="inlineStr">
+        <is>
+          <t>event_1010_b</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B83" s="28" t="inlineStr">
+        <is>
+          <t>小草被水花嚇到轉身就逃，表情驚慌。</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D83" s="28" t="inlineStr">
+        <is>
+          <t>event_1010_c</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="inlineStr">
+        <is>
+          <t>小草混在整齊的菜苗裡假裝是蔬菜，農夫拿水管澆水還點頭稱讚。</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>農夫</t>
+        </is>
+      </c>
+      <c r="D84" s="28" t="inlineStr">
+        <is>
+          <t>event_2001_a</t>
+        </is>
+      </c>
+      <c r="E84" s="28" t="n">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B85" s="28" t="inlineStr">
+        <is>
+          <t>小草從揮下的鋤頭底下驚險鑽過，衝向田外曬燙的空地。</t>
+        </is>
+      </c>
+      <c r="C85" s="28" t="inlineStr">
+        <is>
+          <t>農夫</t>
+        </is>
+      </c>
+      <c r="D85" s="28" t="inlineStr">
+        <is>
+          <t>event_2001_b</t>
+        </is>
+      </c>
+      <c r="E85" s="28" t="n">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>小草被鋤頭敲了一下仍然站著，倒在翻開的土上曬太陽。</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>農夫</t>
+        </is>
+      </c>
+      <c r="D86" s="28" t="inlineStr">
+        <is>
+          <t>event_2001_c</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="n">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B87" s="28" t="inlineStr">
+        <is>
+          <t>小草跳進水渠，順著急流衝向下游，表情興奮。</t>
+        </is>
+      </c>
+      <c r="C87" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D87" s="28" t="inlineStr">
+        <is>
+          <t>event_2002_a</t>
+        </is>
+      </c>
+      <c r="E87" s="28" t="n">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B88" s="28" t="inlineStr">
+        <is>
+          <t>小草探出身子，用葉子撈起被沖走的瓢蟲，頭頂是大太陽。</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>瓢蟲</t>
+        </is>
+      </c>
+      <c r="D88" s="28" t="inlineStr">
+        <is>
+          <t>event_2002_b</t>
+        </is>
+      </c>
+      <c r="E88" s="28" t="n">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B89" s="28" t="inlineStr">
+        <is>
+          <t>小草沿著乾裂的渠邊快跑，泥土裂成一塊一塊。</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D89" s="28" t="inlineStr">
+        <is>
+          <t>event_2002_c</t>
+        </is>
+      </c>
+      <c r="E89" s="28" t="n">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B90" s="28" t="inlineStr">
+        <is>
+          <t>小草躲在稻草人的影子下休息，一臉舒服。</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>稻草人</t>
+        </is>
+      </c>
+      <c r="D90" s="28" t="inlineStr">
+        <is>
+          <t>event_2003_a</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B91" s="28" t="inlineStr">
+        <is>
+          <t>小草和幾隻麻雀在大太陽下偷吃稻穀。</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>麻雀</t>
+        </is>
+      </c>
+      <c r="D91" s="28" t="inlineStr">
+        <is>
+          <t>event_2003_b</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="inlineStr">
+        <is>
+          <t>小草踩著稻草人的斗笠高高跳起，稻草人被弄得歪七扭八。</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>稻草人</t>
+        </is>
+      </c>
+      <c r="D92" s="28" t="inlineStr">
+        <is>
+          <t>event_2003_c</t>
+        </is>
+      </c>
+      <c r="E92" s="28" t="n">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B93" s="28" t="inlineStr">
+        <is>
+          <t>綠燈亮起，小草抬頭挺胸走過斑馬線，把球推回給小朋友。</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="D93" s="28" t="inlineStr">
+        <is>
+          <t>event_2004_a</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="n">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B94" s="28" t="inlineStr">
+        <is>
+          <t>小草衝到馬路中央使出「浪子踢球」，把球送回對面，柏油路冒著熱氣。</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="D94" s="28" t="inlineStr">
+        <is>
+          <t>event_2004_b</t>
+        </is>
+      </c>
+      <c r="E94" s="28" t="n">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B95" s="28" t="inlineStr">
+        <is>
+          <t>小草在滾燙的柏油路上咬牙慢慢爬過馬路。</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D95" s="28" t="inlineStr">
+        <is>
+          <t>event_2004_c</t>
+        </is>
+      </c>
+      <c r="E95" s="28" t="n">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B96" s="28" t="inlineStr">
+        <is>
+          <t>小草抓著會飛的胡蘿蔔飛上半空，俯瞰整片田。</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔</t>
+        </is>
+      </c>
+      <c r="D96" s="28" t="inlineStr">
+        <is>
+          <t>event_2005_a</t>
+        </is>
+      </c>
+      <c r="E96" s="28" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="inlineStr">
+        <is>
+          <t>小草張開葉子擋住兔群，胡蘿蔔趁機飛走，兔子們圍著小草生氣。</t>
+        </is>
+      </c>
+      <c r="C97" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔、兔子</t>
+        </is>
+      </c>
+      <c r="D97" s="28" t="inlineStr">
+        <is>
+          <t>event_2005_b</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B98" s="28" t="inlineStr">
+        <is>
+          <t>小草用閃身步在兔群之間左閃右閃，留下殘影。</t>
+        </is>
+      </c>
+      <c r="C98" s="28" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="D98" s="28" t="inlineStr">
+        <is>
+          <t>event_2005_c</t>
+        </is>
+      </c>
+      <c r="E98" s="28" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B99" s="28" t="inlineStr">
+        <is>
+          <t>牧羊犬開心地舔了小草一口，小草滿身口水。</t>
+        </is>
+      </c>
+      <c r="C99" s="28" t="inlineStr">
+        <is>
+          <t>牧羊犬</t>
+        </is>
+      </c>
+      <c r="D99" s="28" t="inlineStr">
+        <is>
+          <t>event_2006_a</t>
+        </is>
+      </c>
+      <c r="E99" s="28" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B100" s="28" t="inlineStr">
+        <is>
+          <t>小草混在羊群裡一起奔跑，揚起一片塵土。</t>
+        </is>
+      </c>
+      <c r="C100" s="28" t="inlineStr">
+        <is>
+          <t>羊</t>
+        </is>
+      </c>
+      <c r="D100" s="28" t="inlineStr">
+        <is>
+          <t>event_2006_b</t>
+        </is>
+      </c>
+      <c r="E100" s="28" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B101" s="28" t="inlineStr">
+        <is>
+          <t>小草指著遠方騙牧羊犬去追兔子，羊群亂成一團。</t>
+        </is>
+      </c>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>牧羊犬、羊</t>
+        </is>
+      </c>
+      <c r="D101" s="28" t="inlineStr">
+        <is>
+          <t>event_2006_c</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B102" s="28" t="inlineStr">
+        <is>
+          <t>小草漂亮地使出閃身步，青蛙滿意地點頭。</t>
+        </is>
+      </c>
+      <c r="C102" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D102" s="28" t="inlineStr">
+        <is>
+          <t>event_2007_a</t>
+        </is>
+      </c>
+      <c r="E102" s="28" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B103" s="28" t="inlineStr">
+        <is>
+          <t>小草揮動葉子趕走白鷺鷥，青蛙躲在小草身後。</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>青蛙、白鷺鷥</t>
+        </is>
+      </c>
+      <c r="D103" s="28" t="inlineStr">
+        <is>
+          <t>event_2007_b</t>
+        </is>
+      </c>
+      <c r="E103" s="28" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B104" s="28" t="inlineStr">
+        <is>
+          <t>小草把青蛙擠下田埂霸佔位置，自己被太陽曬得發昏。</t>
+        </is>
+      </c>
+      <c r="C104" s="28" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="D104" s="28" t="inlineStr">
+        <is>
+          <t>event_2007_c</t>
+        </is>
+      </c>
+      <c r="E104" s="28" t="n">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B105" s="28" t="inlineStr">
+        <is>
+          <t>學生面前只剩一道綠色殘影，小草已經跑遠了。</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>戴眼鏡的學生</t>
+        </is>
+      </c>
+      <c r="D105" s="28" t="inlineStr">
+        <is>
+          <t>event_2008_b</t>
+        </is>
+      </c>
+      <c r="E105" s="28" t="n">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B106" s="28" t="inlineStr">
+        <is>
+          <t>小草縮起葉子裝成普通的草，學生失望地起身離開。</t>
+        </is>
+      </c>
+      <c r="C106" s="28" t="inlineStr">
+        <is>
+          <t>戴眼鏡的學生</t>
+        </is>
+      </c>
+      <c r="D106" s="28" t="inlineStr">
+        <is>
+          <t>event_2008_c</t>
+        </is>
+      </c>
+      <c r="E106" s="28" t="n">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B107" s="28" t="inlineStr">
+        <is>
+          <t>小草拔腿狂奔，兔子在後面追了一段後停下來。</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="D107" s="28" t="inlineStr">
+        <is>
+          <t>event_2009_b</t>
+        </is>
+      </c>
+      <c r="E107" s="28" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B108" s="28" t="inlineStr">
+        <is>
+          <t>小草指著天空編故事，兔子抬頭找會飛的胡蘿蔔。</t>
+        </is>
+      </c>
+      <c r="C108" s="28" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="D108" s="28" t="inlineStr">
+        <is>
+          <t>event_2009_c</t>
+        </is>
+      </c>
+      <c r="E108" s="28" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B109" s="28" t="inlineStr">
+        <is>
+          <t>小草把一朵漂亮的野花推給小女孩，小女孩抱著花開心離開。</t>
+        </is>
+      </c>
+      <c r="C109" s="28" t="inlineStr">
+        <is>
+          <t>小女孩</t>
+        </is>
+      </c>
+      <c r="D109" s="28" t="inlineStr">
+        <is>
+          <t>event_2010_b</t>
+        </is>
+      </c>
+      <c r="E109" s="28" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B110" s="28" t="inlineStr">
+        <is>
+          <t>小草趴在滾燙的地上躲起來，小女孩從旁邊走過。</t>
+        </is>
+      </c>
+      <c r="C110" s="28" t="inlineStr">
+        <is>
+          <t>小女孩</t>
+        </is>
+      </c>
+      <c r="D110" s="28" t="inlineStr">
+        <is>
+          <t>event_2010_c</t>
+        </is>
+      </c>
+      <c r="E110" s="28" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B111" s="28" t="inlineStr">
+        <is>
+          <t>小草鑽進沙子裡只露出葉尖，熱風從上方吹過。</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D111" s="28" t="inlineStr">
+        <is>
+          <t>event_3001_a</t>
+        </is>
+      </c>
+      <c r="E111" s="28" t="n">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B112" s="28" t="inlineStr">
+        <is>
+          <t>小草頂著熱風往前衝，葉子被吹得乾枯捲曲。</t>
+        </is>
+      </c>
+      <c r="C112" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D112" s="28" t="inlineStr">
+        <is>
+          <t>event_3001_b</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="n">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B113" s="28" t="inlineStr">
+        <is>
+          <t>小草呆站在沙地上發呆，頭頂太陽高照。</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D113" s="28" t="inlineStr">
+        <is>
+          <t>event_3001_c</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="n">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="inlineStr">
+        <is>
+          <t>老仙人掌教小草把根扎深，小草認真聽講。</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>仙人掌</t>
+        </is>
+      </c>
+      <c r="D114" s="28" t="inlineStr">
+        <is>
+          <t>event_3002_a</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="n">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B115" s="28" t="inlineStr">
+        <is>
+          <t>小草穿上用仙人掌刺做的盔甲，仙人掌怒目瞪著它。</t>
+        </is>
+      </c>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>仙人掌</t>
+        </is>
+      </c>
+      <c r="D115" s="28" t="inlineStr">
+        <is>
+          <t>event_3002_b</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="n">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B116" s="28" t="inlineStr">
+        <is>
+          <t>小草揮葉趕走啃仙人掌的蜥蜴，仙人掌欣慰地微笑。</t>
+        </is>
+      </c>
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>仙人掌、蜥蜴</t>
+        </is>
+      </c>
+      <c r="D116" s="28" t="inlineStr">
+        <is>
+          <t>event_3002_c</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="n">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B117" s="28" t="inlineStr">
+        <is>
+          <t>小草捏著鼻子，從乾掉的排水溝裡鑽過去。</t>
+        </is>
+      </c>
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D117" s="28" t="inlineStr">
+        <is>
+          <t>event_3003_a</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B118" s="28" t="inlineStr">
+        <is>
+          <t>小草沿著人行道的磚縫全速衝刺，留下速度線。</t>
+        </is>
+      </c>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D118" s="28" t="inlineStr">
+        <is>
+          <t>event_3003_b</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B119" s="28" t="inlineStr">
+        <is>
+          <t>小草揮葉把一隻迷路的麻雀趕得更遠，得意地叉腰。</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>麻雀</t>
+        </is>
+      </c>
+      <c r="D119" s="28" t="inlineStr">
+        <is>
+          <t>event_3003_c</t>
+        </is>
+      </c>
+      <c r="E119" s="28" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B120" s="28" t="inlineStr">
+        <is>
+          <t>小草從室外機底下全速衝過，身上冒著一點煙。</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D120" s="28" t="inlineStr">
+        <is>
+          <t>event_3004_a</t>
+        </is>
+      </c>
+      <c r="E120" s="28" t="n">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B121" s="28" t="inlineStr">
+        <is>
+          <t>小草躲在室外機後面被熱風烤著，咬牙忍耐。</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D121" s="28" t="inlineStr">
+        <is>
+          <t>event_3004_b</t>
+        </is>
+      </c>
+      <c r="E121" s="28" t="n">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B122" s="28" t="inlineStr">
+        <is>
+          <t>小草咬斷室外機的電線，整排冷氣停擺，路人抬頭生氣。</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>路人</t>
+        </is>
+      </c>
+      <c r="D122" s="28" t="inlineStr">
+        <is>
+          <t>event_3004_c</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="n">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B123" s="28" t="inlineStr">
+        <is>
+          <t>流浪貓在小草身上打滾，小草被壓扁又彈回來。</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>流浪貓</t>
+        </is>
+      </c>
+      <c r="D123" s="28" t="inlineStr">
+        <is>
+          <t>event_3005_a</t>
+        </is>
+      </c>
+      <c r="E123" s="28" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B124" s="28" t="inlineStr">
+        <is>
+          <t>小草用葉子幫貓搔下巴，貓舒服地瞇起眼睛。</t>
+        </is>
+      </c>
+      <c r="C124" s="28" t="inlineStr">
+        <is>
+          <t>流浪貓</t>
+        </is>
+      </c>
+      <c r="D124" s="28" t="inlineStr">
+        <is>
+          <t>event_3005_b</t>
+        </is>
+      </c>
+      <c r="E124" s="28" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B125" s="28" t="inlineStr">
+        <is>
+          <t>小草踮著腳尖，從熟睡的貓旁邊偷偷溜走。</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>流浪貓</t>
+        </is>
+      </c>
+      <c r="D125" s="28" t="inlineStr">
+        <is>
+          <t>event_3005_c</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B126" s="28" t="inlineStr">
+        <is>
+          <t>夕陽下，小草坐在石頭旁聽它說大地的故事。</t>
+        </is>
+      </c>
+      <c r="C126" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D126" s="28" t="inlineStr">
+        <is>
+          <t>event_3006_a</t>
+        </is>
+      </c>
+      <c r="E126" s="28" t="n">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B127" s="28" t="inlineStr">
+        <is>
+          <t>小草把石頭踢下坡，石頭一路滾一路罵。</t>
+        </is>
+      </c>
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D127" s="28" t="inlineStr">
+        <is>
+          <t>event_3006_b</t>
+        </is>
+      </c>
+      <c r="E127" s="28" t="n">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B128" s="28" t="inlineStr">
+        <is>
+          <t>小草揮手道別往前跑，石頭在後方喊話。</t>
+        </is>
+      </c>
+      <c r="C128" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="D128" s="28" t="inlineStr">
+        <is>
+          <t>event_3006_c</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="n">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B129" s="28" t="inlineStr">
+        <is>
+          <t>小草騎在鴿子背上，飛越城市的屋頂。</t>
+        </is>
+      </c>
+      <c r="C129" s="28" t="inlineStr">
+        <is>
+          <t>鴿子</t>
+        </is>
+      </c>
+      <c r="D129" s="28" t="inlineStr">
+        <is>
+          <t>event_3007_a</t>
+        </is>
+      </c>
+      <c r="E129" s="28" t="n">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B130" s="28" t="inlineStr">
+        <is>
+          <t>小草抱著麵包屑，被一群鴿子圍著啄。</t>
+        </is>
+      </c>
+      <c r="C130" s="28" t="inlineStr">
+        <is>
+          <t>鴿子</t>
+        </is>
+      </c>
+      <c r="D130" s="28" t="inlineStr">
+        <is>
+          <t>event_3007_b</t>
+        </is>
+      </c>
+      <c r="E130" s="28" t="n">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B131" s="28" t="inlineStr">
+        <is>
+          <t>小草把麵包屑分給搶不到的小雛鳥。</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>雛鳥</t>
+        </is>
+      </c>
+      <c r="D131" s="28" t="inlineStr">
+        <is>
+          <t>event_3007_c</t>
+        </is>
+      </c>
+      <c r="E131" s="28" t="n">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B132" s="28" t="inlineStr">
+        <is>
+          <t>小草用閃身步穿梭在車陣之間，留下殘影。</t>
+        </is>
+      </c>
+      <c r="C132" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D132" s="28" t="inlineStr">
+        <is>
+          <t>event_3008_a</t>
+        </is>
+      </c>
+      <c r="E132" s="28" t="n">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B133" s="28" t="inlineStr">
+        <is>
+          <t>小草卡在輪胎的紋路裡，輪胎差點壓下來。</t>
+        </is>
+      </c>
+      <c r="C133" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D133" s="28" t="inlineStr">
+        <is>
+          <t>event_3008_b</t>
+        </is>
+      </c>
+      <c r="E133" s="28" t="n">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B134" s="28" t="inlineStr">
+        <is>
+          <t>小草把蟋蟀踢進車底，頭也不回地離開。</t>
+        </is>
+      </c>
+      <c r="C134" s="28" t="inlineStr">
+        <is>
+          <t>蟋蟀</t>
+        </is>
+      </c>
+      <c r="D134" s="28" t="inlineStr">
+        <is>
+          <t>event_3008_c</t>
+        </is>
+      </c>
+      <c r="E134" s="28" t="n">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B135" s="28" t="inlineStr">
+        <is>
+          <t>小草在未乾的水泥上留下一個小小的草腳印。</t>
+        </is>
+      </c>
+      <c r="C135" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D135" s="28" t="inlineStr">
+        <is>
+          <t>event_3009_a</t>
+        </is>
+      </c>
+      <c r="E135" s="28" t="n">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B136" s="28" t="inlineStr">
+        <is>
+          <t>小草推倒告示牌砸出一條捷徑，工人們在後面生氣。</t>
+        </is>
+      </c>
+      <c r="C136" s="28" t="inlineStr">
+        <is>
+          <t>工人</t>
+        </is>
+      </c>
+      <c r="D136" s="28" t="inlineStr">
+        <is>
+          <t>event_3009_b</t>
+        </is>
+      </c>
+      <c r="E136" s="28" t="n">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B137" s="28" t="inlineStr">
+        <is>
+          <t>小草擋在水泥前，提醒小螞蟻繞道走。</t>
+        </is>
+      </c>
+      <c r="C137" s="28" t="inlineStr">
+        <is>
+          <t>螞蟻</t>
+        </is>
+      </c>
+      <c r="D137" s="28" t="inlineStr">
+        <is>
+          <t>event_3009_c</t>
+        </is>
+      </c>
+      <c r="E137" s="28" t="n">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B138" s="28" t="inlineStr">
+        <is>
+          <t>小草緊緊抱住一塊大石頭，沙塵從身邊呼嘯而過。</t>
+        </is>
+      </c>
+      <c r="C138" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D138" s="28" t="inlineStr">
+        <is>
+          <t>event_3010_a</t>
+        </is>
+      </c>
+      <c r="E138" s="28" t="n">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B139" s="28" t="inlineStr">
+        <is>
+          <t>小草跑在沙塵暴的前方，和它賽跑。</t>
+        </is>
+      </c>
+      <c r="C139" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D139" s="28" t="inlineStr">
+        <is>
+          <t>event_3010_b</t>
+        </is>
+      </c>
+      <c r="E139" s="28" t="n">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B140" s="28" t="inlineStr">
+        <is>
+          <t>小草張開葉子護住幾顆小種子，沙子打在它背上。</t>
+        </is>
+      </c>
+      <c r="C140" s="28" t="inlineStr">
+        <is>
+          <t>小種子</t>
+        </is>
+      </c>
+      <c r="D140" s="28" t="inlineStr">
+        <is>
+          <t>event_3010_c</t>
+        </is>
+      </c>
+      <c r="E140" s="28" t="n">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B141" s="28" t="inlineStr">
+        <is>
+          <t>小草混在九層塔堆裡，攤販老闆正要抓一把丟進油鍋。</t>
+        </is>
+      </c>
+      <c r="C141" s="28" t="inlineStr">
+        <is>
+          <t>攤販</t>
+        </is>
+      </c>
+      <c r="D141" s="28" t="inlineStr">
+        <is>
+          <t>event_3011_a</t>
+        </is>
+      </c>
+      <c r="E141" s="28" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B142" s="28" t="inlineStr">
+        <is>
+          <t>小草偷吃一口粉圓，整株精神百倍。</t>
+        </is>
+      </c>
+      <c r="C142" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D142" s="28" t="inlineStr">
+        <is>
+          <t>event_3011_b</t>
+        </is>
+      </c>
+      <c r="E142" s="28" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B143" s="28" t="inlineStr">
+        <is>
+          <t>小草揮葉幫攤販趕走蒼蠅，攤販完全沒注意到它。</t>
+        </is>
+      </c>
+      <c r="C143" s="28" t="inlineStr">
+        <is>
+          <t>攤販</t>
+        </is>
+      </c>
+      <c r="D143" s="28" t="inlineStr">
+        <is>
+          <t>event_3011_c</t>
+        </is>
+      </c>
+      <c r="E143" s="28" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B144" s="28" t="inlineStr">
+        <is>
+          <t>小草像忍者一樣，在屋簷之間飛奔跳躍。</t>
+        </is>
+      </c>
+      <c r="C144" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D144" s="28" t="inlineStr">
+        <is>
+          <t>event_3012_a</t>
+        </is>
+      </c>
+      <c r="E144" s="28" t="n">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B145" s="28" t="inlineStr">
+        <is>
+          <t>小草躺在發燙的鐵皮屋頂上曬日光浴。</t>
+        </is>
+      </c>
+      <c r="C145" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D145" s="28" t="inlineStr">
+        <is>
+          <t>event_3012_b</t>
+        </is>
+      </c>
+      <c r="E145" s="28" t="n">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B146" s="28" t="inlineStr">
+        <is>
+          <t>小草偷吃鳥巢裡的蟲，鳥媽媽飛回來氣得大叫。</t>
+        </is>
+      </c>
+      <c r="C146" s="28" t="inlineStr">
+        <is>
+          <t>鳥媽媽</t>
+        </is>
+      </c>
+      <c r="D146" s="28" t="inlineStr">
+        <is>
+          <t>event_3012_c</t>
+        </is>
+      </c>
+      <c r="E146" s="28" t="n">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B147" s="28" t="inlineStr">
+        <is>
+          <t>小草在鹽堆上奔跑練腳力，鹽粒四處飛濺。</t>
+        </is>
+      </c>
+      <c r="C147" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D147" s="28" t="inlineStr">
+        <is>
+          <t>event_3013_a</t>
+        </is>
+      </c>
+      <c r="E147" s="28" t="n">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B148" s="28" t="inlineStr">
+        <is>
+          <t>小草和招潮蟹比腕力，小草險勝。</t>
+        </is>
+      </c>
+      <c r="C148" s="28" t="inlineStr">
+        <is>
+          <t>招潮蟹</t>
+        </is>
+      </c>
+      <c r="D148" s="28" t="inlineStr">
+        <is>
+          <t>event_3013_b</t>
+        </is>
+      </c>
+      <c r="E148" s="28" t="n">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B149" s="28" t="inlineStr">
+        <is>
+          <t>小草把招潮蟹的大螯藏在鹽堆後面偷笑，招潮蟹四處尋找。</t>
+        </is>
+      </c>
+      <c r="C149" s="28" t="inlineStr">
+        <is>
+          <t>招潮蟹</t>
+        </is>
+      </c>
+      <c r="D149" s="28" t="inlineStr">
+        <is>
+          <t>event_3013_c</t>
+        </is>
+      </c>
+      <c r="E149" s="28" t="n">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B150" s="28" t="inlineStr">
+        <is>
+          <t>小草掛在蒲公英的絨毛種子上，飄過城市街道。</t>
+        </is>
+      </c>
+      <c r="C150" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D150" s="28" t="inlineStr">
+        <is>
+          <t>event_3014_a</t>
+        </is>
+      </c>
+      <c r="E150" s="28" t="n">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B151" s="28" t="inlineStr">
+        <is>
+          <t>小草用身體幫老蒲公英擋住熱風，種子安穩落地。</t>
+        </is>
+      </c>
+      <c r="C151" s="28" t="inlineStr">
+        <is>
+          <t>老蒲公英</t>
+        </is>
+      </c>
+      <c r="D151" s="28" t="inlineStr">
+        <is>
+          <t>event_3014_b</t>
+        </is>
+      </c>
+      <c r="E151" s="28" t="n">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B152" s="28" t="inlineStr">
+        <is>
+          <t>小草一口氣把老蒲公英的絨毛吹光，老蒲公英愣在原地。</t>
+        </is>
+      </c>
+      <c r="C152" s="28" t="inlineStr">
+        <is>
+          <t>老蒲公英</t>
+        </is>
+      </c>
+      <c r="D152" s="28" t="inlineStr">
+        <is>
+          <t>event_3014_c</t>
+        </is>
+      </c>
+      <c r="E152" s="28" t="n">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B153" s="28" t="inlineStr">
+        <is>
+          <t>小草揮手道別，胡蘿蔔在天上繞了一圈後消失在雲裡。</t>
+        </is>
+      </c>
+      <c r="C153" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔</t>
+        </is>
+      </c>
+      <c r="D153" s="28" t="inlineStr">
+        <is>
+          <t>event_3015_b</t>
+        </is>
+      </c>
+      <c r="E153" s="28" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B154" s="28" t="inlineStr">
+        <is>
+          <t>小草繼續在地上奔跑，天上的胡蘿蔔越來越小。</t>
+        </is>
+      </c>
+      <c r="C154" s="28" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔</t>
+        </is>
+      </c>
+      <c r="D154" s="28" t="inlineStr">
+        <is>
+          <t>event_3015_c</t>
+        </is>
+      </c>
+      <c r="E154" s="28" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B155" s="28" t="inlineStr">
+        <is>
+          <t>小草看了看狹窄的裂縫，搖搖頭從旁邊跑過。</t>
+        </is>
+      </c>
+      <c r="C155" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D155" s="28" t="inlineStr">
+        <is>
+          <t>event_3016_b</t>
+        </is>
+      </c>
+      <c r="E155" s="28" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B156" s="28" t="inlineStr">
+        <is>
+          <t>小草清掉裂縫裡的垃圾，土裡隱約冒出一點新芽。</t>
+        </is>
+      </c>
+      <c r="C156" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D156" s="28" t="inlineStr">
+        <is>
+          <t>event_3016_c</t>
+        </is>
+      </c>
+      <c r="E156" s="28" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B157" s="28" t="inlineStr">
+        <is>
+          <t>小草朝著遠方的地平線繼續奔跑。</t>
+        </is>
+      </c>
+      <c r="C157" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D157" s="28" t="inlineStr">
+        <is>
+          <t>event_3017_b</t>
+        </is>
+      </c>
+      <c r="E157" s="28" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B158" s="28" t="inlineStr">
+        <is>
+          <t>小草在荒地上打盹醒來，伸懶腰，太陽高掛。</t>
+        </is>
+      </c>
+      <c r="C158" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D158" s="28" t="inlineStr">
+        <is>
+          <t>event_3017_c</t>
+        </is>
+      </c>
+      <c r="E158" s="28" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B159" s="28" t="inlineStr">
+        <is>
+          <t>小草指出別的青草，爺爺笑著摸摸它。</t>
+        </is>
+      </c>
+      <c r="C159" s="28" t="inlineStr">
+        <is>
+          <t>爺爺</t>
+        </is>
+      </c>
+      <c r="D159" s="28" t="inlineStr">
+        <is>
+          <t>event_3018_b</t>
+        </is>
+      </c>
+      <c r="E159" s="28" t="n">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B160" s="28" t="inlineStr">
+        <is>
+          <t>竹籃差點罩到小草頭上，小草趁爺爺不注意快跑。</t>
+        </is>
+      </c>
+      <c r="C160" s="28" t="inlineStr">
+        <is>
+          <t>爺爺</t>
+        </is>
+      </c>
+      <c r="D160" s="28" t="inlineStr">
+        <is>
+          <t>event_3018_c</t>
+        </is>
+      </c>
+      <c r="E160" s="28" t="n">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B161" s="28" t="inlineStr">
+        <is>
+          <t>小草在一旁偷學手藝，把自己捲得更結實。</t>
+        </is>
+      </c>
+      <c r="C161" s="28" t="inlineStr">
+        <is>
+          <t>老師傅</t>
+        </is>
+      </c>
+      <c r="D161" s="28" t="inlineStr">
+        <is>
+          <t>event_3019_b</t>
+        </is>
+      </c>
+      <c r="E161" s="28" t="n">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B162" s="28" t="inlineStr">
+        <is>
+          <t>小草拖著剪刀狂奔，老師傅在後面追。</t>
+        </is>
+      </c>
+      <c r="C162" s="28" t="inlineStr">
+        <is>
+          <t>老師傅</t>
+        </is>
+      </c>
+      <c r="D162" s="28" t="inlineStr">
+        <is>
+          <t>event_3019_c</t>
+        </is>
+      </c>
+      <c r="E162" s="28" t="n">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B163" s="28" t="inlineStr">
+        <is>
+          <t>小草坐在沙灘上遠遠看著大海，被海風吹得有點乾。</t>
+        </is>
+      </c>
+      <c r="C163" s="28" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D163" s="28" t="inlineStr">
+        <is>
+          <t>event_3020_b</t>
+        </is>
+      </c>
+      <c r="E163" s="28" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="28" t="inlineStr">
+        <is>
+          <t>選項結果</t>
+        </is>
+      </c>
+      <c r="B164" s="28" t="inlineStr">
+        <is>
+          <t>小草把擱淺的小魚推回海裡，小魚甩著尾巴游走。</t>
+        </is>
+      </c>
+      <c r="C164" s="28" t="inlineStr">
+        <is>
+          <t>小魚</t>
+        </is>
+      </c>
+      <c r="D164" s="28" t="inlineStr">
+        <is>
+          <t>event_3020_c</t>
+        </is>
+      </c>
+      <c r="E164" s="28" t="n">
+        <v>3020</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E164">
+    <sortState ref="A5:E164">
+      <sortCondition ref="A4:A164"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="2">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5518,15 +9686,1526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" style="29" min="1" max="1"/>
+    <col width="10" customWidth="1" style="29" min="2" max="2"/>
+    <col width="50" customWidth="1" style="29" min="3" max="3"/>
+    <col hidden="1" width="16" customWidth="1" style="29" min="4" max="4"/>
+    <col width="9" customWidth="1" style="29" min="5" max="6"/>
+    <col width="24" customWidth="1" style="29" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
+    <row r="1" ht="45" customHeight="1" s="29">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>「外觀設定」用來讓 Codex 每次畫出的角色長相一致：產圖時，把該圖出場人物的外觀設定接在提詞後面。人物名稱與「插圖需求」分頁的出場人物欄一致。「招式」不是人物，是小草的動作；圖中出現該招式時，把它的外觀設定一起接在提詞後面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1" s="29">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>人物</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>外觀設定（產圖用）</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>出場事件</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>出場圖數</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>是否已有參考圖</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25.5" customHeight="1" s="29">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>小草</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>主角</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>一株有兩隻小腳、圓眼睛的擬人化綠色小草，頭頂兩片葉子會隨心情擺動。</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="n">
+        <v>160</v>
+      </c>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>每張圖都有；外觀依美術定案調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25.5" customHeight="1" s="29">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>講話石頭</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>重複角色</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>灰色圓滾滾的大石頭，有瞇瞇眼和會說話的嘴，表面長著一點青苔。</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>1005、3006</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>會滾著追上小草</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" s="29">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>青蛙</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>重複角色</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>圓胖的綠色青蛙，綁著小小的武術頭帶，常雙手抱胸擺出師父架勢。</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>1009、2007</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>教小草閃身步的師父</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" s="29">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>會飛的胡蘿蔔</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>重複角色</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>橘色的胡蘿蔔，頭頂綠葉像翅膀一樣拍動，表情開朗愛冒險。</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>2005、3015</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>3015 為特殊結局</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25.5" customHeight="1" s="29">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>白色長耳兔子，鼻子一直抽動。</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>2005、2009</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>2005 為一群</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>小朋友</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>一群穿運動服、追著足球大叫的國小學生。</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>1007、2004</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+    </row>
+    <row r="10" ht="38.25" customHeight="1" s="29">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>閃身步</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>招式</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>小草左右快速閃動，身後留下一串綠色殘影。</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>1009、2005、2007、2008、3008</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>青蛙教的閃避招式</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>螞蟻</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>重複角色</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>小小的紅褐色螞蟻，成群排隊行動，常扛著食物。</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>1002、3009</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>多隻出場</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>農夫</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>戴斗笠、扛著鋤頭的中年農夫。</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>小女孩</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>綁雙馬尾、穿洋裝的小女孩。</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>2010 為特殊結局</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>爺爺</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>戴草帽、提著竹籃的慈祥老爺爺。</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>3018 為特殊結局</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>蝸牛</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>背著螺旋殼、動作慢吞吞的蝸牛，眼睛長在觸角上。</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>流浪貓</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>懶洋洋的橘色虎斑流浪貓。</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>仙人掌</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>年老的綠色仙人掌，刺像白鬍子一樣。</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>戴眼鏡的學生</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>戴圓框眼鏡、拿著放大鏡的國小學生。</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>2008 為特殊結局</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>攤販</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>綁頭巾、圍圍裙的台灣夜市攤販。</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>老師傅</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>留著白鬍子、手很巧的編草老師傅。</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>牛</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>黑白花紋的大乳牛。</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>蚯蚓</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>粉紅色的蚯蚓。</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>牧羊犬</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>黑白相間的邊境牧羊犬。</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>羊</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>毛茸茸的白色綿羊。</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>成群出場</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>鴿子</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>灰色的城市鴿子。</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>3007 為一群</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" s="29">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>招潮蟹</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>一邊大螯特別大的招潮蟹。</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1" s="29">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>老蒲公英</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>頭頂只剩一圈白絨毛、彎著腰、有白眉毛的老蒲公英。</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>稻草人</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>物件</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>戴斗笠、張開雙臂的稻草人。</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>麻雀</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>重複角色</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>圓滾滾的褐色小麻雀。</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>2003、3003</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>兩個事件不一定是同一隻</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1" s="29">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>瓢蟲</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>紅底黑點的小瓢蟲。</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>1003、2002</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="inlineStr">
+        <is>
+          <t>1003 為多隻</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="13.5" customHeight="1" s="29">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>蒲公英</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>開著黃花、帶著溫柔笑臉的蒲公英。</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>浪子踢球</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>招式</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>小草單腳飛起、瀟灑甩頭，把球踢出一道漂亮的弧線。</t>
+        </is>
+      </c>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>1007、2004</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="inlineStr">
+        <is>
+          <t>特殊的踢球招式</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>路人</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>城市裡的一般路人，當作背景。</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="inlineStr">
+        <is>
+          <t>背景角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>工人</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>戴黃色安全帽、穿反光背心的工地工人。</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>夜市人潮</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>擠在夜市裡的人群，當作背景。</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="inlineStr">
+        <is>
+          <t>背景角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>小孩</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>人類</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>背著書包的小學生，書包上掛著草蜢。</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="28" t="inlineStr">
+        <is>
+          <t>3019 特殊結局圖</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>白鷺鷥</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
+        <is>
+          <t>白色長腳的白鷺鷥。</t>
+        </is>
+      </c>
+      <c r="D37" s="28" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>蜥蜴</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>沙色的小蜥蜴。</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>雛鳥</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>毛茸茸的小雛鳥。</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>蟋蟀</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>黑褐色的小蟋蟀。</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>鳥媽媽</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="inlineStr">
+        <is>
+          <t>褐色的鳥媽媽，生氣時羽毛炸開。</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="inlineStr">
+        <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>小魚</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="inlineStr">
+        <is>
+          <t>小小的銀色魚。</t>
+        </is>
+      </c>
+      <c r="D42" s="28" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>另一株小草</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>和主角相似，但顏色較淡、沒有腳的普通小草。</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>花圃的花</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="inlineStr">
+        <is>
+          <t>一排枯萎後慢慢抬起頭的小花，有小臉。</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>小種子</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="inlineStr">
+        <is>
+          <t>幾顆圓圓的小種子，有小小的臉。</t>
+        </is>
+      </c>
+      <c r="D45" s="28" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G45">
+    <sortState ref="A4:G45">
+      <sortCondition descending="1" ref="E3:E45"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="14.42578125" customWidth="1" style="29" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>初始濕度</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>准許濕度</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>0~100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Demo 5輪</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>實際 15輪結束</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Demo版濕度選項</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>一個-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>一個-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>一個-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>兩個-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>兩個-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>兩個-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>三個-10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <cols>
+    <col width="18" customWidth="1" style="29" min="1" max="1"/>
+    <col width="60" customWidth="1" style="29" min="2" max="2"/>
+    <col width="40" customWidth="1" style="29" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" s="29">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>一、表格共通規則</t>
@@ -5548,13 +11227,13 @@
       </c>
       <c r="C2" s="8" t="n"/>
     </row>
-    <row r="3" ht="51" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="51" customHeight="1" s="29">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>前三列</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>第 1 列：中文名稱（給人看）
 第 2 列：key（程式讀取用，不可改名）
@@ -5564,42 +11243,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>int 欄位</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>只能填整數，不可有小數點或文字</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>空白格</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>代表「沒有」，不要填 0、無、- 之類的字</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>備註欄</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>沒有 key 的欄位（第 2 列空白）程式不讀，可自由寫</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
+    <row r="7"/>
+    <row r="8" ht="16.5" customHeight="1" s="29">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>二、屬性代碼</t>
@@ -5625,84 +11305,85 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="10" ht="25.5" customHeight="1" s="29">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>mor</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>善良值</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>可為負數：正數越大越善良，0＝中立，負數越小越邪惡</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>hmd</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>濕度</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>0～100，初始 50，降到 0 以下死亡</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>spd</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>最低 0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>tgh</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>韌度</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>最低 0</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="25.5" customHeight="1" s="29">
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>所有欄位一律使用以上 4 個小寫代碼，不可用其他寫法（如 tol、hum、speed）</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
+      <c r="C14" s="28" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="16.5" customHeight="1" s="29">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t>三、變動值 choice_x_offset</t>
@@ -5729,149 +11410,149 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>格式</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>屬性:正負號數值</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>hmd:-20</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>正負號</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>一定要寫，+ 也不能省略</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>spd:+10（✗ spd:10）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>數值</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>只能是整數</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>hmd:-15（✗ hmd:-1.5）</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>多個屬性</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>用 ; 分隔，最後不加 ;</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>spd:+10;hmd:-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>空白字元</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>不可有任何空格</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>✗ spd: +10 ; hmd:-20</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>重複</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>同一格裡同一屬性只能出現一次</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>✗ hmd:-10;hmd:-10</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>順序</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>固定依 mor → hmd → spd → tgh 排列</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>mor:-15;hmd:-10;tgh:+10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>沒有變動</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>留空</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="28" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>與文案對應</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>文案寫到的變化，offset 一定要有；offset 有的變化，文案也要看得出來</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>喝到水 → 要有 hmd:+xx</t>
         </is>
@@ -5891,66 +11572,67 @@
       <c r="C27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>只減濕度</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>hmd:-20</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>跑得快但變乾</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>hmd:-20;spd:+10</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="30" ht="25.5" customHeight="1" s="29">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>做壞事，變強也變邪惡</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>mor:-15;tgh:+10</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>幫助別人</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>mor:+10;hmd:-10</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>喝到水</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>hmd:+20</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
+    <row r="33"/>
+    <row r="34" ht="16.5" customHeight="1" s="29">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>四、需求 choice_x_require</t>
@@ -5977,151 +11659,152 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>格式</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>屬性 + 比較符號 + 數值</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>spd&gt;=30</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>比較符號</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>只能用 &gt;=（至少）或 &lt;=（至多）</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>mor&lt;=-20（夠邪惡才能選）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>多個條件</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>用 ; 分隔，全部滿足才可選</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>spd&gt;=30;tgh&gt;=20</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>範圍</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>同一屬性可同時寫上下限</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>mor&gt;=-10;mor&lt;=10（中立才能選）</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>負數</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>只有 mor 可以寫負數門檻</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>✗ hmd&gt;=-10</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>順序</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t>固定依 mor → hmd → spd → tgh 排列</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>沒有需求</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>留空，代表任何時候都可選</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>不滿足時</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>選項照樣顯示，但不可點選</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="44" ht="38.25" customHeight="1" s="29">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>善良值需求原則</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>±5 的小事不設需求；+10 的善事設 mor&gt;=-10（太邪惡就不肯幫忙）；-10 的壞事設 mor&lt;=10（太善良就下不了手）；-15 以上的大壞事設 mor&lt;=-5（越陷越深）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="45" ht="16.5" customHeight="1" s="29">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>至少一個可選</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>每個事件至少要有一個沒有需求的選項，避免三個都鎖住</t>
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="46"/>
+    <row r="47" ht="16.5" customHeight="1" s="29">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>五、結局 choice_x_end</t>
@@ -6148,59 +11831,60 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>內容</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>填 title_list 的 title_id（整數）</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>觸發</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>選了這個選項就直接結束遊戲，給該稱號</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>沒有結局</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="28" t="inlineStr">
         <is>
           <t>留空</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+    <row r="52" ht="16.5" customHeight="1" s="29">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>對應</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="28" t="inlineStr">
         <is>
           <t>填的 ID 必須存在於 title_list</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="25.5" customHeight="1">
+    <row r="53"/>
+    <row r="54" ht="25.5" customHeight="1" s="29">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>六、event_list 其他欄位</t>
@@ -6222,91 +11906,92 @@
       </c>
       <c r="C55" s="8" t="n"/>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="56" ht="25.5" customHeight="1" s="29">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>事件 ID，千位數＝階段（1xxx 第 1 階段、2xxx 第 2 階段、3xxx 第 3 階段），不可重複</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="25.5" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+    <row r="57" ht="25.5" customHeight="1" s="29">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>unlock_event_num</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>解鎖所需事件數：已經歷 N 個事件後，此事件才會進入抽選池</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="25.5" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="58" ht="25.5" customHeight="1" s="29">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>event_desc</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="28" t="inlineStr">
         <is>
           <t>事件敘述（題目本身）（不限字數）</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="25.5" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+    <row r="59" ht="25.5" customHeight="1" s="29">
+      <c r="A59" s="28" t="inlineStr">
         <is>
           <t>choice_x_desc</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="28" t="inlineStr">
         <is>
           <t>選項文案：最多 14 字（含標點符號，剛好 14 字可以），只暗示需求與後果，不直接寫數值。只有這三欄有字數限制</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="60" ht="16.5" customHeight="1" s="29">
+      <c r="A60" s="28" t="inlineStr">
         <is>
           <t>choice_x_result</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="28" t="inlineStr">
         <is>
           <t>選後回饋：選完後顯示的微敘事＋提示，例「你變得更溼潤了，前方乾燥地帶可能更難」（不限字數）</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+    <row r="61" ht="25.5" customHeight="1" s="29">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>event_image</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="28" t="inlineStr">
         <is>
           <t>事件發生時顯示的圖片。命名：event_{事件ID}，例 event_1001，不含副檔名。圖片由 Codex image generate 產生</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="16.5" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="62" ht="16.5" customHeight="1" s="29">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>choice_x_image</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="28" t="inlineStr">
         <is>
           <t>選完該選項後顯示的圖片。命名：event_{事件ID}_{a/b/c}，例 event_1001_a，不含副檔名；結局選項的圖也填這裡。圖片由 Codex image generate 產生</t>
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="63"/>
+    <row r="64" ht="16.5" customHeight="1" s="29">
       <c r="A64" s="6" t="inlineStr">
         <is>
           <t>七、階段規則（濕度）</t>
@@ -6333,70 +12018,71 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>1（1xxx）</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
+    <row r="67" ht="16.5" customHeight="1" s="29">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>2（2xxx）</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="28" t="inlineStr">
         <is>
           <t>B、C</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>3（3xxx）</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="28" t="inlineStr">
         <is>
           <t>A、B、C</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="25.5" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
+    <row r="69" ht="25.5" customHeight="1" s="29">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="B69" s="28" t="n"/>
+      <c r="C69" s="28" t="inlineStr">
         <is>
           <t>有填 end 的特殊結局選項不受此限</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="25.5" customHeight="1">
+    <row r="70"/>
+    <row r="71" ht="25.5" customHeight="1" s="29">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>八、稱號 title_list</t>
@@ -6418,13 +12104,13 @@
       </c>
       <c r="C72" s="8" t="n"/>
     </row>
-    <row r="73" ht="25.5" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+    <row r="73" ht="25.5" customHeight="1" s="29">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>判定順序</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B73" s="28" t="inlineStr">
         <is>
           <t>1. 遊戲中選了有 end 的選項 → 給該特殊結局稱號
 2. 否則結算時看屬性 → 找 reach_* 三欄都吻合的那一列</t>
@@ -6432,200 +12118,225 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>reach_*</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B74" s="28" t="inlineStr">
         <is>
           <t>填條件字串，格式同 require（例：mor&gt;=10）；空白＝中立／未達標</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="25.5" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+    <row r="75" ht="25.5" customHeight="1" s="29">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>吻合規則</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B75" s="28" t="inlineStr">
         <is>
           <t>有填的條件都要成立；空白欄的屬性不可符合該欄出現過的任何條件（mor 空白＝不善也不惡）</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
+    <row r="76" ht="16.5" customHeight="1" s="29">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>ID 0</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B76" s="28" t="inlineStr">
         <is>
           <t>三欄皆空白＝無為的草</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="77" ht="25.5" customHeight="1" s="29">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>ID 0～11</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B77" s="28" t="inlineStr">
         <is>
           <t>善良值 3 種（善／中立／惡）× 速度 2 種 × 韌度 2 種 = 12 種組合，不可重複、不可缺漏</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16.5" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
+    <row r="78" ht="16.5" customHeight="1" s="29">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>特殊結局</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B78" s="28" t="inlineStr">
         <is>
           <t>ID 與觸發它的事件 ID 相同（如 2008）；reach_* 留空；3021 為備用</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>title_desc</t>
+        </is>
+      </c>
+      <c r="B79" s="28" t="inlineStr">
+        <is>
+          <t>結局描述：結局畫面顯示的敘事文字，2～3 句，不限字數</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16.5" customHeight="1" s="29">
+      <c r="A80" s="28" t="inlineStr">
+        <is>
+          <t>title_condition</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="inlineStr">
+        <is>
+          <t>達成條件：給人看的條件說明。一般稱號依 reach_* 寫出三個屬性的範圍；特殊結局寫出觸發的事件、選項與需求。改了 reach_* 或觸發選項的需求時要一起更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82" ht="25.5" customHeight="1" s="29">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>九、達標門檻（依 title_list 的 reach_*）</t>
         </is>
       </c>
-      <c r="B80" s="7" t="n"/>
-      <c r="C80" s="7" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>條件</t>
         </is>
       </c>
-      <c r="C81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="25.5" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="C83" s="8" t="n"/>
+    </row>
+    <row r="84" ht="16.5" customHeight="1" s="29">
+      <c r="A84" s="28" t="inlineStr">
         <is>
           <t>善</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B84" s="28" t="inlineStr">
         <is>
           <t>mor&gt;=10</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>惡</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B85" s="28" t="inlineStr">
         <is>
           <t>mor&lt;=-10</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
+    <row r="86" ht="16.5" customHeight="1" s="29">
+      <c r="A86" s="28" t="inlineStr">
         <is>
           <t>速度達標</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>spd&gt;=20</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>spd&gt;=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="25.5" customHeight="1" s="29">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>韌度達標</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>tgh&gt;=20</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="16.5" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="B87" s="28" t="inlineStr">
+        <is>
+          <t>tgh&gt;=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16.5" customHeight="1" s="29">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>濕度</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B88" s="28" t="inlineStr">
         <is>
           <t>不列入稱號判定（濕度是遊戲結束條件）</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="25.5" customHeight="1"/>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
+    <row r="89" ht="25.5" customHeight="1" s="29"/>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>十、請 AI 填寫時的提醒</t>
         </is>
       </c>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
-    </row>
-    <row r="89" ht="25.5" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+    </row>
+    <row r="91" ht="25.5" customHeight="1" s="29">
+      <c r="A91" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B91" s="28" t="inlineStr">
         <is>
           <t>先決定 offset，再依 offset 寫文案與回饋，避免數值和文字對不上</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B92" s="28" t="inlineStr">
         <is>
           <t>遵守第七節的階段濕度規則</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B93" s="28" t="inlineStr">
         <is>
           <t>文案不出現數字，只用敘事暗示；選項文案（choice_a/b/c_desc）不可超過 14 字（含標點），事件敘述與回饋不限字數</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B94" s="28" t="inlineStr">
         <is>
           <t>填完後對照本頁規則逐格檢查</t>
         </is>

--- a/Doc/FGJ 2026表格_v2.xlsx
+++ b/Doc/FGJ 2026表格_v2.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'插圖需求'!$A$4:$E$164</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人物列表'!$A$3:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'人物列表'!$A$3:$H$45</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>一根胡蘿蔔拍著葉子從頭上飛過，後面追著一群兔子。</t>
+          <t>一根胡蘿蔔拍著翅膀從頭上飛過，後面追著一群兔子。</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -5575,12 +5575,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="13.5" customHeight="1" s="29">
       <c r="K32" s="14" t="n"/>
     </row>
@@ -6024,7 +6018,7 @@
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>一根拍著葉子飛行的胡蘿蔔從頭上飛過，後面追著一群兔子。</t>
+          <t>一根拍著翅膀飛行的胡蘿蔔從頭上飛過，後面追著一群兔子。</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
@@ -6074,7 +6068,7 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>稻田邊，青蛙師父雙手抱胸，要考小草的閃身步。</t>
+          <t>稻田邊，青蛙師父一臉嚴肅地蹲坐著，要考小草的閃身步。</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
@@ -9686,7 +9680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="14" customWidth="1" style="29" min="1" max="1"/>
@@ -9694,7 +9688,7 @@
     <col width="50" customWidth="1" style="29" min="3" max="3"/>
     <col hidden="1" width="16" customWidth="1" style="29" min="4" max="4"/>
     <col width="9" customWidth="1" style="29" min="5" max="6"/>
-    <col width="24" customWidth="1" style="29" min="7" max="7"/>
+    <col width="30" customWidth="1" style="29" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" s="29">
@@ -9705,7 +9699,7 @@
       </c>
       <c r="B1" s="28" t="inlineStr">
         <is>
-          <t>「外觀設定」用來讓 Codex 每次畫出的角色長相一致：產圖時，把該圖出場人物的外觀設定接在提詞後面。人物名稱與「插圖需求」分頁的出場人物欄一致。「招式」不是人物，是小草的動作；圖中出現該招式時，把它的外觀設定一起接在提詞後面。</t>
+          <t>「外觀設定」用來讓 Codex 每次畫出的角色長相一致：產圖時，把該圖出場人物的外觀設定接在提詞後面。人物名稱與「插圖需求」分頁的出場人物欄一致。「招式」不是人物，是小草的動作；圖中出現該招式時，把它的外觀設定一起接在提詞後面。有參考圖的角色（CharacterReference/ 資料夾），產圖時請一併附上參考圖。</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9734,12 @@
           <t>是否已有參考圖</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>參考圖</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -9771,7 +9770,8 @@
         <v>160</v>
       </c>
       <c r="F4" s="28" t="n"/>
-      <c r="G4" s="28" t="inlineStr">
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>每張圖都有；外觀依美術定案調整</t>
         </is>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>灰色圓滾滾的大石頭，有瞇瞇眼和會說話的嘴，表面長著一點青苔。</t>
+          <t>灰色多角形的大石頭，臉上是瞇起的眼睛和張大的嘴，深灰色粗描邊。</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
@@ -9808,6 +9808,11 @@
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
+          <t>CharacterReference/講話石頭.jpg</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
           <t>會滾著追上小草</t>
         </is>
       </c>
@@ -9825,7 +9830,7 @@
       </c>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>圓胖的綠色青蛙，綁著小小的武術頭帶，常雙手抱胸擺出師父架勢。</t>
+          <t>圓胖、趴著的淺綠色青蛙，米白色的大下巴，兩顆大眼睛凸在頭頂，深綠色粗描邊，背上有深綠斑點。</t>
         </is>
       </c>
       <c r="D6" s="28" t="inlineStr">
@@ -9841,7 +9846,12 @@
           <t>有</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>CharacterReference/青蛙.jpg</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>教小草閃身步的師父</t>
         </is>
@@ -9860,7 +9870,7 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>橘色的胡蘿蔔，頭頂綠葉像翅膀一樣拍動，表情開朗愛冒險。</t>
+          <t>橘色蛋形的胡蘿蔔，沒有手腳，背後有一對白色天使翅膀，頭頂的綠葉圍成光環，表情瞇眼淡定。</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
@@ -9876,7 +9886,12 @@
           <t>有</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>CharacterReference/會飛的胡蘿蔔.jpg</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>3015 為特殊結局</t>
         </is>
@@ -9907,7 +9922,8 @@
         <v>7</v>
       </c>
       <c r="F8" s="28" t="n"/>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>2005 為一群</t>
         </is>
@@ -9939,6 +9955,7 @@
       </c>
       <c r="F9" s="28" t="n"/>
       <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
     </row>
     <row r="10" ht="38.25" customHeight="1" s="29">
       <c r="A10" s="28" t="inlineStr">
@@ -9969,7 +9986,8 @@
           <t>有</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>青蛙教的閃避招式</t>
         </is>
@@ -10000,7 +10018,8 @@
         <v>4</v>
       </c>
       <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>多隻出場</t>
         </is>
@@ -10032,6 +10051,7 @@
       </c>
       <c r="F12" s="28" t="n"/>
       <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="28" t="inlineStr">
@@ -10058,7 +10078,8 @@
         <v>4</v>
       </c>
       <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>2010 為特殊結局</t>
         </is>
@@ -10089,7 +10110,8 @@
         <v>4</v>
       </c>
       <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>3018 為特殊結局</t>
         </is>
@@ -10121,6 +10143,7 @@
       </c>
       <c r="F15" s="28" t="n"/>
       <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="28" t="inlineStr">
@@ -10148,6 +10171,7 @@
       </c>
       <c r="F16" s="28" t="n"/>
       <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="28" t="inlineStr">
@@ -10175,6 +10199,7 @@
       </c>
       <c r="F17" s="28" t="n"/>
       <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="28" t="inlineStr">
@@ -10201,7 +10226,8 @@
         <v>3</v>
       </c>
       <c r="F18" s="28" t="n"/>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>2008 為特殊結局</t>
         </is>
@@ -10233,6 +10259,7 @@
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
@@ -10260,6 +10287,7 @@
       </c>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
+      <c r="H20" s="28" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
@@ -10287,6 +10315,7 @@
       </c>
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="28" t="inlineStr">
@@ -10314,6 +10343,7 @@
       </c>
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
@@ -10341,6 +10371,7 @@
       </c>
       <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
@@ -10367,7 +10398,8 @@
         <v>3</v>
       </c>
       <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>成群出場</t>
         </is>
@@ -10398,7 +10430,8 @@
         <v>3</v>
       </c>
       <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>3007 為一群</t>
         </is>
@@ -10430,6 +10463,7 @@
       </c>
       <c r="F26" s="28" t="n"/>
       <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27" ht="13.5" customHeight="1" s="29">
       <c r="A27" s="25" t="inlineStr">
@@ -10444,7 +10478,7 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>頭頂只剩一圈白絨毛、彎著腰、有白眉毛的老蒲公英。</t>
+          <t>和「蒲公英」參考圖同一種造型，但絨毛稀疏只剩最後一圈，表情疲憊、莖微微彎曲。</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -10456,7 +10490,12 @@
         <v>3</v>
       </c>
       <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n"/>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>CharacterReference/蒲公英.jpg（共用）</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
@@ -10484,6 +10523,7 @@
       </c>
       <c r="F28" s="28" t="n"/>
       <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
@@ -10510,7 +10550,8 @@
         <v>2</v>
       </c>
       <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="28" t="n"/>
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>兩個事件不一定是同一隻</t>
         </is>
@@ -10541,7 +10582,8 @@
         <v>2</v>
       </c>
       <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="28" t="n"/>
+      <c r="H30" s="28" t="inlineStr">
         <is>
           <t>1003 為多隻</t>
         </is>
@@ -10560,7 +10602,7 @@
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>開著黃花、帶著溫柔笑臉的蒲公英。</t>
+          <t>白色蓬鬆的絨毛球蒲公英，中間是淺褐色的圓臉帶著微笑，綠色花萼和細長的莖。</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -10571,8 +10613,17 @@
       <c r="E31" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="28" t="n"/>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>CharacterReference/蒲公英.jpg</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="28" t="inlineStr">
@@ -10599,7 +10650,8 @@
         <v>2</v>
       </c>
       <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>特殊的踢球招式</t>
         </is>
@@ -10630,7 +10682,8 @@
         <v>1</v>
       </c>
       <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>背景角色</t>
         </is>
@@ -10662,6 +10715,7 @@
       </c>
       <c r="F34" s="28" t="n"/>
       <c r="G34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="28" t="inlineStr">
@@ -10688,7 +10742,8 @@
         <v>1</v>
       </c>
       <c r="F35" s="28" t="n"/>
-      <c r="G35" s="28" t="inlineStr">
+      <c r="G35" s="28" t="n"/>
+      <c r="H35" s="28" t="inlineStr">
         <is>
           <t>背景角色</t>
         </is>
@@ -10719,7 +10774,8 @@
         <v>1</v>
       </c>
       <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="inlineStr">
+      <c r="G36" s="28" t="n"/>
+      <c r="H36" s="28" t="inlineStr">
         <is>
           <t>3019 特殊結局圖</t>
         </is>
@@ -10751,6 +10807,7 @@
       </c>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="28" t="inlineStr">
@@ -10778,6 +10835,7 @@
       </c>
       <c r="F38" s="28" t="n"/>
       <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="28" t="inlineStr">
@@ -10805,6 +10863,7 @@
       </c>
       <c r="F39" s="28" t="n"/>
       <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="28" t="inlineStr">
@@ -10832,6 +10891,7 @@
       </c>
       <c r="F40" s="28" t="n"/>
       <c r="G40" s="28" t="n"/>
+      <c r="H40" s="28" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="28" t="inlineStr">
@@ -10859,6 +10919,7 @@
       </c>
       <c r="F41" s="28" t="n"/>
       <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="28" t="inlineStr">
@@ -10886,6 +10947,7 @@
       </c>
       <c r="F42" s="28" t="n"/>
       <c r="G42" s="28" t="n"/>
+      <c r="H42" s="28" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="28" t="inlineStr">
@@ -10913,6 +10975,7 @@
       </c>
       <c r="F43" s="28" t="n"/>
       <c r="G43" s="28" t="n"/>
+      <c r="H43" s="28" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="28" t="inlineStr">
@@ -10940,6 +11003,7 @@
       </c>
       <c r="F44" s="28" t="n"/>
       <c r="G44" s="28" t="n"/>
+      <c r="H44" s="28" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="28" t="inlineStr">
@@ -10967,9 +11031,10 @@
       </c>
       <c r="F45" s="28" t="n"/>
       <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G45">
+  <autoFilter ref="A3:H45">
     <sortState ref="A4:G45">
       <sortCondition descending="1" ref="E3:E45"/>
     </sortState>
@@ -11278,7 +11343,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1" s="29">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -11382,7 +11446,6 @@
       </c>
       <c r="C14" s="28" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="16.5" customHeight="1" s="29">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -11631,7 +11694,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="16.5" customHeight="1" s="29">
       <c r="A34" s="6" t="inlineStr">
         <is>
@@ -11803,7 +11865,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47" ht="16.5" customHeight="1" s="29">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -11883,7 +11944,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54" ht="25.5" customHeight="1" s="29">
       <c r="A54" s="6" t="inlineStr">
         <is>
@@ -11990,7 +12050,6 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
     <row r="64" ht="16.5" customHeight="1" s="29">
       <c r="A64" s="6" t="inlineStr">
         <is>
@@ -12081,7 +12140,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71" ht="25.5" customHeight="1" s="29">
       <c r="A71" s="6" t="inlineStr">
         <is>
@@ -12201,7 +12259,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
     <row r="82" ht="25.5" customHeight="1" s="29">
       <c r="A82" s="6" t="inlineStr">
         <is>
